--- a/Teacher Resources (Start Here)/06_STARLAB_Master_Print_Packet_Index.xlsx
+++ b/Teacher Resources (Start Here)/06_STARLAB_Master_Print_Packet_Index.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Re787411c930046a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print Packet Index" sheetId="2" r:id="R7978dcc6409c4216"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Print Queue" sheetId="3" r:id="R39178fa68a0e42ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Unit" sheetId="4" r:id="Ra2b73ef3b44745c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Type Key" sheetId="5" r:id="R194cf09786264db6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R34c44a9595d64e46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print Packet Index" sheetId="2" r:id="R55b5b93884bc4974"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Print Queue" sheetId="3" r:id="R18f97d74571e4589"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Unit" sheetId="4" r:id="R4aeea3ddf42148e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Type Key" sheetId="5" r:id="R664d5d85eaf247cc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -104,35 +104,15 @@
     <x:t xml:space="preserve">Deck 03</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 2 / Week 4</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Unit 1; Unit 2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 1 Student Handout 4: Research Ethics and Integrity Agreement
-Unit 2 Student Handout 9: Safety and Risk Assessment
-Unit 2 Student Handout 10: Ethics and Approval Screening
-Unit 2 Appendix E: Risk Assessment Matrix
-Unit 2 Appendix F: Safety and Ethics Red Flags
-Unit 2 Appendix H: Project Approval Checklist</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Introduced early as course culture; revisited during formal project approval.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Experimental Design and Engineering Design Basics</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Deck 04</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 2 / Week 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Use first as a foundation lesson; revisit when students plan variables, criteria, and evidence.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Building a Formal Research Plan</x:t>
   </x:si>
   <x:si>
@@ -142,140 +122,34 @@
     <x:t xml:space="preserve">Unit 2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 2 Student Handout 1: Project Refinement Workshop
-Unit 2 Student Handout 2: Background Research Notes
-Unit 2 Student Handout 3: Hypothesis and Design Criteria Builder
-Unit 2 Student Handout 4: Variables, Controls, Criteria, and Constraints Organizer
-Unit 2 Student Handout 5: Evidence Planning Tool
-Unit 2 Student Handout 6: Materials and Equipment Planner
-Unit 2 Student Handout 7: Procedure and Testing Protocol Builder
-Unit 2 Student Handout 8: Data Collection Plan
-Unit 2 Student Handout 9: Safety and Risk Assessment
-Unit 2 Student Handout 10: Ethics and Approval Screening
-Unit 2 Student Handout 11: Project Timeline Planner
-Unit 2 Student Handout 12: Formal Research Plan Template
-Unit 2 Student Handout 13: Research Plan Conference Form
-Unit 2 Appendix H: Project Approval Checklist</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Project approval tracking sheet
-Mentor review template, if applicable</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">The main Unit 2 planning and approval deck.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Pilot Testing</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Deck 06</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 3 / Week 5</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Unit 3</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 3 Student Handout 1: Pilot Test Plan
-Unit 3 Student Handout 4: Pilot Test Reflection and Troubleshooting Log
-Unit 3 Student Handout 5: Method Revision Decision Chart
-Unit 3 Appendix A: What Is Pilot Testing?
-Unit 3 Appendix C: Safety Check Before Testing
-Unit 3 Appendix E: Troubleshooting Sentence Frames</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 3 Student Handout 3: Daily Research Journal Entry Template
-Unit 3 Appendix B: Research Journal Standards</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Launches the transition from planning to action.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Research Journals and Scientific Documentation</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Deck 07</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 3 / Weeks 6–16</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 3 Student Handout 2: Research Journal Setup
-Unit 3 Student Handout 3: Daily Research Journal Entry Template
-Unit 3 Student Handout 4: Pilot Test Reflection and Troubleshooting Log
-Unit 3 Appendix B: Research Journal Standards</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 3 Student Handout 9: Weekly Progress Check-In
-Unit 3 Student Handout 19: Research Journal Self-Assessment
-Unit 3 Appendix Q: File and Data Organization Standards</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Introduce at journal setup; revisit throughout the long research phase.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Troubleshooting and Responsible Project Pivots</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Deck 08</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 3 / Week 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 3 / Weeks 10, 13</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 3 Student Handout 4: Pilot Test Reflection and Troubleshooting Log
-Unit 3 Student Handout 5: Method Revision Decision Chart
-Unit 3 Student Handout 6: Revised Procedure Template
-Unit 3 Student Handout 11: Troubleshooting Conference Prep
-Unit 3 Student Handout 12: Mentor or Expert Feedback Log
-Unit 3 Appendix D: Types of Research Problems
-Unit 3 Appendix E: Troubleshooting Sentence Frames
-Unit 3 Appendix K: Responsible Project Pivots</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 3 Student Handout 9: Weekly Progress Check-In
-Unit 3 Student Handout 15: Post-Progress Report Action Plan
-Unit 3 Appendix P: Recovery Plan Options</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Use whenever a project stalls, pivots, or needs structured revision.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Data Organization: Raw Data vs. Clean Data</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Deck 09</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 4 / Week 17</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 3 / Week 15–16 bridge</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Unit 3; Unit 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 4 Student Handout 1: Raw Data Inventory
-Unit 4 Student Handout 2: Clean Data Set Builder
-Unit 4 Student Handout 3: Data Cleaning Decision Log
-Unit 4 Student Handout 4: Week 17 Data Audit
-Unit 4 Appendix A: Raw Data vs. Clean Data
-Unit 4 Appendix B: Data Cleaning Rules
-Unit 4 Appendix C: Common Data Organization Problems</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 3 Student Handout 17: Data Audit and Organization Checklist
-Unit 3 Student Handout 18: Unit 3 Readiness for Analysis Review
-Unit 3 Appendix Q: File and Data Organization Standards
-Unit 3 Appendix R: Raw Data vs. Clean Data</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Primary Unit 4 launch deck; can be previewed near the end of Unit 3.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Choosing the Right Data Analysis Method</x:t>
@@ -470,12 +344,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Deck 19</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 6 / Week 34</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Final course closure deck. No next deck after this.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Unit</x:t>
@@ -2020,7 +1888,7 @@
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="132" hidden="0" customHeight="1">
       <x:c r="A4" s="5">
         <x:v>3.0</x:v>
       </x:c>
@@ -2030,199 +1898,237 @@
       <x:c r="C4" s="5" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="s">
+      <x:c r="D4" s="8" t="str">
+        <x:v>Unit 1 / Week 1</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="str">
+        <x:v>Unit 2 / Week 4</x:v>
+      </x:c>
+      <x:c r="F4" s="8" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F4" s="5" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G4" s="5" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H4" s="5" t="str">
-        <x:v>District-supplied safety, human-participant, privacy, media, fieldwork, equipment, chemical, drone, IRB/SRC, or other local forms as applicable</x:v>
-      </x:c>
-      <x:c r="I4" s="5" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+      <x:c r="G4" s="8" t="str">
+        <x:v>Week 1 required:
+Unit 1 Student Handout 4: Research Ethics and Integrity Agreement
+Week 4 revisit required:
+Unit 2 Student Handout 9: Safety and Risk Assessment
+Unit 2 Student Handout 10: Ethics and Approval Screening
+Unit 2 Appendix E: Risk Assessment Matrix
+Unit 2 Appendix F: Safety and Ethics Red Flags
+Unit 2 Appendix H: Project Approval Checklist</x:v>
+      </x:c>
+      <x:c r="H4" s="8" t="str">
+        <x:v>District-supplied safety, human-participant, privacy, media, fieldwork, equipment, chemical, drone, IRB/SRC, or other local forms as applicable.</x:v>
+      </x:c>
+      <x:c r="I4" s="8" t="str">
+        <x:v>Introduce in Week 1 as course culture; revisit in Week 4 during formal project approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A5" s="5">
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E5" s="5" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F5" s="5" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G5" s="5" t="str">
-        <x:v>Unit 1 Student Handout 5: Experimental Design Practice
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>Unit 1 / Week 2</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str">
+        <x:v>Unit 2 / Week 3</x:v>
+      </x:c>
+      <x:c r="F5" s="8" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G5" s="8" t="str">
+        <x:v>Week 2 required:
+Unit 1 Student Handout 5: Experimental Design Practice
 Unit 1 Appendix D: Experimental Design Vocabulary
 Unit 1 Appendix G: Engineering Design Problem Guide
+Week 3 revisit required:
 Unit 2 Student Handout 3: Hypothesis and Design Criteria Builder
 Unit 2 Student Handout 4: Variables, Controls, Criteria, and Constraints Organizer
 Unit 2 Student Handout 5: Evidence Planning Tool</x:v>
       </x:c>
-      <x:c r="H5" s="5" t="str">
-        <x:v>Unit 1 Appendix I: Optional Project Card Sorting Activity
+      <x:c r="H5" s="8" t="str">
+        <x:v>Week 2 optional / teacher reference:
+Unit 1 Appendix I: Optional Project Card Sorting Activity
 Mini-investigation supplies</x:v>
       </x:c>
-      <x:c r="I5" s="5" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+      <x:c r="I5" s="8" t="str">
+        <x:v>Use first as a Week 2 foundation lesson; revisit during Week 3 planning.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A6" s="5">
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E6" s="5"/>
-      <x:c r="F6" s="5" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G6" s="5" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H6" s="5" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I6" s="5" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="str">
+        <x:v>Unit 2 / Weeks 3-4</x:v>
+      </x:c>
+      <x:c r="E6" s="8" t="str"/>
+      <x:c r="F6" s="8" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="str">
+        <x:v>Week 3 required:
+Unit 2 Student Handouts 1-5
+Unit 2 Appendices A-D
+Week 4 required:
+Unit 2 Student Handouts 6-13
+Unit 2 Appendices E-H</x:v>
+      </x:c>
+      <x:c r="H6" s="8" t="str">
+        <x:v>Week 4 optional / teacher reference:
+Unit 2 Appendix I: Mentor Feedback Request Template
+Unit 2 Appendix J: Sample Completed Planning Excerpt
+District-supplied approval and safety forms as applicable</x:v>
+      </x:c>
+      <x:c r="I6" s="8" t="str">
+        <x:v>The main Unit 2 planning and approval deck. The Week 3 and Week 4 packets are separated here to match the implementation calendar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A7" s="5">
         <x:v>6.0</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D7" s="5" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E7" s="5"/>
-      <x:c r="F7" s="5" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G7" s="5" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H7" s="5" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="I7" s="5" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D7" s="8" t="str">
+        <x:v>Unit 3 / Week 5</x:v>
+      </x:c>
+      <x:c r="E7" s="8" t="str"/>
+      <x:c r="F7" s="8" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
+        <x:v>Week 5 required weekly packet (shared with Deck 7):
+Unit 3 Student Handouts 1-3
+Unit 3 Appendices A-C</x:v>
+      </x:c>
+      <x:c r="H7" s="8" t="str"/>
+      <x:c r="I7" s="8" t="str">
+        <x:v>Launches pilot testing. Week 6 troubleshooting materials are introduced with Deck 8, not printed early with this deck.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A8" s="5">
         <x:v>7.0</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D8" s="5" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E8" s="5" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F8" s="5" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G8" s="5" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H8" s="5" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="I8" s="5" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="str">
+        <x:v>Unit 3 / Week 5</x:v>
+      </x:c>
+      <x:c r="E8" s="8" t="str">
+        <x:v>Unit 3 / Weeks 6-16 as needed</x:v>
+      </x:c>
+      <x:c r="F8" s="8" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="str">
+        <x:v>Week 5 required weekly packet (shared with Deck 6):
+Unit 3 Student Handouts 1-3
+Unit 3 Appendices A-C</x:v>
+      </x:c>
+      <x:c r="H8" s="8" t="str">
+        <x:v>Later optional / teacher reference:
+Unit 3 Student Handout 9: Weekly Progress Check-In
+Unit 3 Student Handout 19: Research Journal Self-Assessment
+Unit 3 Appendix Q: File and Data Organization Standards</x:v>
+      </x:c>
+      <x:c r="I8" s="8" t="str">
+        <x:v>Introduce journal setup in Week 5; revisit documentation routines throughout Unit 3.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A9" s="5">
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E9" s="5" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F9" s="5" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G9" s="5" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H9" s="5" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I9" s="5" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D9" s="8" t="str">
+        <x:v>Unit 3 / Week 6</x:v>
+      </x:c>
+      <x:c r="E9" s="8" t="str">
+        <x:v>Unit 3 / Weeks 7, 10, and 13 as needed</x:v>
+      </x:c>
+      <x:c r="F9" s="8" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="str">
+        <x:v>Week 6 required:
+Unit 3 Student Handout 4: Pilot Test Reflection and Troubleshooting Log
+Unit 3 Student Handout 5: Method Revision Decision Chart
+Unit 3 Appendix D: Types of Research Problems
+Unit 3 Appendix E: Troubleshooting Sentence Frames</x:v>
+      </x:c>
+      <x:c r="H9" s="8" t="str">
+        <x:v>Week 7 revisit: Student Handouts 6-7; Appendices F-G
+Week 10 revisit: Student Handouts 11-12; Appendices K-L are optional / teacher reference
+Week 13 recovery use: Student Handout 15; Appendix P is optional / teacher reference</x:v>
+      </x:c>
+      <x:c r="I9" s="8" t="str">
+        <x:v>Use whenever a project stalls, pivots, or needs structured revision. Later-week resources remain in their assigned weekly packets.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A10" s="5">
         <x:v>9.0</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>62</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D10" s="5" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E10" s="5" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F10" s="5" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G10" s="5" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H10" s="5" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="I10" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D10" s="8" t="str">
+        <x:v>Unit 3 / Week 15; Unit 4 / Week 17</x:v>
+      </x:c>
+      <x:c r="E10" s="8" t="str">
+        <x:v>Unit 3 / Week 16 revisit</x:v>
+      </x:c>
+      <x:c r="F10" s="8" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G10" s="8" t="str">
+        <x:v>Week 15 required:
+Unit 3 Student Handout 17: Data Audit and Organization Checklist
+Unit 3 Appendices Q-R
+Week 16 required (Deck 9 revisit):
+Unit 3 Student Handout 18: Unit 3 Readiness for Analysis Review
+Unit 3 Student Handout 19: Research Journal Self-Assessment
+Week 17 required:
+Unit 4 Student Handouts 1-4
+Unit 4 Appendices A-C</x:v>
+      </x:c>
+      <x:c r="H10" s="8" t="str">
+        <x:v>Week 16 optional / teacher reference:
+Unit 3 Appendices S-U</x:v>
+      </x:c>
+      <x:c r="I10" s="8" t="str">
+        <x:v>Use as the Week 15 data-organization bridge, revisit in Week 16 for readiness, and teach again at the Unit 4 launch.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2230,26 +2136,26 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="B11" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C11" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D11" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G11" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I11" s="5" t="s">
-        <x:v>76</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2257,17 +2163,17 @@
         <x:v>11.0</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>77</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C12" s="5" t="s">
-        <x:v>78</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D12" s="5" t="s">
-        <x:v>79</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G12" s="5" t="str">
         <x:v>Unit 4 Student Handout 9: Graph and Visual Selection Tool
@@ -2277,10 +2183,10 @@
 Unit 4 Appendices H-K</x:v>
       </x:c>
       <x:c r="H12" s="5" t="s">
-        <x:v>80</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I12" s="5" t="s">
-        <x:v>81</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2288,19 +2194,19 @@
         <x:v>12.0</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>82</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C13" s="5" t="s">
-        <x:v>83</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D13" s="5" t="s">
-        <x:v>79</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E13" s="5" t="s">
-        <x:v>84</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F13" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G13" s="5" t="str">
         <x:v>Unit 4 Student Handout 11: Error, Uncertainty, and Limitations Review
@@ -2312,7 +2218,7 @@
 Project-specific uncertainty examples</x:v>
       </x:c>
       <x:c r="I13" s="5" t="s">
-        <x:v>85</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2320,26 +2226,26 @@
         <x:v>13.0</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>86</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C14" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D14" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E14" s="5"/>
       <x:c r="F14" s="5" t="s">
-        <x:v>89</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G14" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H14" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I14" s="5" t="s">
-        <x:v>92</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2347,28 +2253,28 @@
         <x:v>14.0</x:v>
       </x:c>
       <x:c r="B15" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C15" s="5" t="s">
-        <x:v>94</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D15" s="5" t="s">
-        <x:v>95</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E15" s="5" t="s">
-        <x:v>96</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F15" s="5" t="s">
-        <x:v>97</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G15" s="5" t="s">
-        <x:v>98</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H15" s="5" t="s">
-        <x:v>99</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I15" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2376,26 +2282,26 @@
         <x:v>15.0</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>101</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C16" s="5" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D16" s="5" t="s">
-        <x:v>103</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E16" s="5"/>
       <x:c r="F16" s="5" t="s">
-        <x:v>89</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G16" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H16" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="I16" s="5" t="s">
-        <x:v>106</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2403,19 +2309,19 @@
         <x:v>16.0</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>107</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C17" s="5" t="s">
-        <x:v>108</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D17" s="5" t="s">
-        <x:v>109</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E17" s="5" t="s">
-        <x:v>110</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F17" s="5" t="s">
-        <x:v>111</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G17" s="5" t="str">
         <x:v>Unit 5 Student Handout 10: Presentation Planning Guide
@@ -2428,7 +2334,7 @@
 Unit 6 Appendices I-K (teacher event references)</x:v>
       </x:c>
       <x:c r="I17" s="5" t="s">
-        <x:v>112</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2436,19 +2342,19 @@
         <x:v>17.0</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>113</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C18" s="5" t="s">
-        <x:v>114</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D18" s="5" t="s">
-        <x:v>109</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E18" s="5" t="s">
-        <x:v>115</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F18" s="5" t="s">
-        <x:v>111</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G18" s="5" t="str">
         <x:v>Unit 5 Student Handouts 10-11
@@ -2459,7 +2365,7 @@
         <x:v>Unit 6 Appendix L: final summative Oral Presentation rubric (teacher scoring reference)</x:v>
       </x:c>
       <x:c r="I18" s="5" t="s">
-        <x:v>116</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2467,56 +2373,56 @@
         <x:v>18.0</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
-        <x:v>117</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C19" s="5" t="s">
-        <x:v>118</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D19" s="5" t="s">
-        <x:v>119</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E19" s="5"/>
       <x:c r="F19" s="5" t="s">
-        <x:v>120</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G19" s="5" t="s">
-        <x:v>121</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H19" s="5" t="s">
-        <x:v>122</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="I19" s="5" t="s">
-        <x:v>123</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A20" s="5">
         <x:v>19.0</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>124</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C20" s="5" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="D20" s="5" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="E20" s="5"/>
-      <x:c r="F20" s="5" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G20" s="5" t="str">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D20" s="8" t="str">
+        <x:v>Unit 6 / Week 34</x:v>
+      </x:c>
+      <x:c r="E20" s="8" t="str"/>
+      <x:c r="F20" s="8" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G20" s="8" t="str">
         <x:v>Unit 6 Student Handout 15: Final Research Process Reflection
 Unit 6 Student Handout 16: STARLAB Portfolio Checklist
 Unit 6 Student Handout 18: Course Feedback and Legacy Reflection</x:v>
       </x:c>
-      <x:c r="H20" s="5" t="str">
+      <x:c r="H20" s="8" t="str">
         <x:v>Unit 6 Student Handout 17: Optional Next-Step Plan
-Unit 6 Appendices O-S (optional or teacher reference)</x:v>
-      </x:c>
-      <x:c r="I20" s="5" t="s">
-        <x:v>127</x:v>
+Unit 6 Appendices O-S: optional / teacher reference</x:v>
+      </x:c>
+      <x:c r="I20" s="8" t="str">
+        <x:v>Final course closure deck. No next deck follows.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1"/>
@@ -5161,19 +5067,19 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>129</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C1" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D1" s="4" t="s">
-        <x:v>131</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E1" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -5181,81 +5087,81 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>133</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C2" s="5" t="s">
-        <x:v>134</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D2" s="5" t="s">
-        <x:v>135</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E2" s="5" t="s">
-        <x:v>136</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>137</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
-        <x:v>138</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D3" s="5" t="s">
-        <x:v>139</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E3" s="5" t="s">
-        <x:v>140</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>141</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>142</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>143</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>144</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>145</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>146</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>147</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>148</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="5" t="s">
-        <x:v>89</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>149</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>150</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>151</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
         <x:v>Student Handouts 1-11; Appendixes A-O and Q-S; Unit 6 Appendix L is the final oral rubric</x:v>
@@ -5263,19 +5169,19 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="5" t="s">
-        <x:v>120</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>152</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
         <x:v>Presentation, required public showcase, Q&amp;A, reflection, portfolio, and next steps</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>153</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>154</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1"/>
@@ -6274,10 +6180,10 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="4" t="s">
-        <x:v>155</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>156</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -6285,7 +6191,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>157</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6293,7 +6199,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>158</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -6301,7 +6207,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>159</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6309,7 +6215,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>160</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6317,7 +6223,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>161</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -6330,18 +6236,18 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="s">
-        <x:v>162</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>163</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="5" t="s">
-        <x:v>164</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>165</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="10">

--- a/Teacher Resources (Start Here)/06_STARLAB_Master_Print_Packet_Index.xlsx
+++ b/Teacher Resources (Start Here)/06_STARLAB_Master_Print_Packet_Index.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R34c44a9595d64e46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print Packet Index" sheetId="2" r:id="R55b5b93884bc4974"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Print Queue" sheetId="3" r:id="R18f97d74571e4589"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Unit" sheetId="4" r:id="R4aeea3ddf42148e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Type Key" sheetId="5" r:id="R664d5d85eaf247cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R2730892ae6044289"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print Packet Index" sheetId="2" r:id="R7f7fed98e2d24fc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Print Queue" sheetId="3" r:id="Ra6dbc8079c654db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Unit" sheetId="4" r:id="R500c174791e84cff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Type Key" sheetId="5" r:id="Rcf33a24bc93742ce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -65,9 +65,6 @@
     <x:t xml:space="preserve">Deck 01</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 1 / Week 1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Unit 1</x:t>
   </x:si>
   <x:si>
@@ -92,9 +89,6 @@
     <x:t xml:space="preserve">Deck 02</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 1 / Week 2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Use after students have generated possible interest areas.</x:t>
   </x:si>
   <x:si>
@@ -158,54 +152,29 @@
     <x:t xml:space="preserve">Deck 10</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 4 / Week 18</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Unit 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 4 Student Handout 5: Data Type and Analysis Match
-Unit 4 Student Handout 6: Data Analysis Plan
-Unit 4 Student Handout 7: Calculation and Statistics Record
-Unit 4 Student Handout 8: Engineering Performance Analysis
-Unit 4 Appendix D: Basic Statistics Guide
-Unit 4 Appendix E: Choosing an Analysis Method
-Unit 4 Appendix F: Engineering and Design Analysis Guide
-Unit 4 Appendix G: Qualitative and Observational Data Guide</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Spreadsheet software access
 Project-specific calculators or analysis tools</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Use once clean data sets are ready.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Graphing and Visual Ethics</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Deck 11</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 4 / Week 19</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Examples of strong and weak graphs
 Spreadsheet or graphing software access</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Pairs with graph construction and visual review.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Error, Uncertainty, and Limitations</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Deck 12</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 4 / Week 20</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Use after initial graphs/calculations; revisit before interpretation.</x:t>
   </x:si>
   <x:si>
@@ -215,60 +184,23 @@
     <x:t xml:space="preserve">Deck 13</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 5 / Week 21</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Unit 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 5 Student Handout 1: Scientific Report Dissection
-Unit 5 Student Handout 2: My Research Report Planning Map
-Unit 5 Appendix A: Scientific Report Section Guide
-Unit 5 Appendix L: Scientific Report Template</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Model report or simplified published paper
 Weak sample report or teacher-created flawed example</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Launches the reporting unit.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Writing the Discussion: Claim, Evidence, Reasoning</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Deck 14</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 5 / Week 25</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 4 / Week 20 bridge</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 4; Unit 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 5 Student Handout 6: Discussion Builder
-Unit 5 Appendix H: Claim-Evidence-Reasoning Guide
-Unit 5 Appendix I: Limitations and Error Analysis Guide
-Unit 4 Student Handout 13: Claim-Evidence-Reasoning Organizer
-Unit 4 Student Handout 15: Interpretation and Conclusion Draft Notes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Student graphs, analysis summaries, and limitation notes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Supports discussion writing; can preview at the end of Unit 4.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Peer Review and Scientific Revision</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Deck 15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 5 / Week 27</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Unit 5 Student Handout 8: Peer Review Protocol
@@ -289,12 +221,6 @@
     <x:t xml:space="preserve">Deck 16</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 5 / Week 28</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 6 / Week 32</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Unit 5; Unit 6</x:t>
   </x:si>
   <x:si>
@@ -307,37 +233,13 @@
     <x:t xml:space="preserve">Deck 17</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 6 / Weeks 29–30</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Use for the transition from report/visual aid to spoken explanation.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Answering Questions Like a Scientist</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Deck 18</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unit 6 / Week 31</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Unit 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit 6 Student Handout 7: Q&amp;A Preparation Guide
-Unit 6 Student Handout 8: Mock Q&amp;A Reflection
-Unit 6 Student Handout 9: Evidence Defense Organizer
-Unit 6 Appendix F: Question Bank for Research Presentations
-Unit 6 Appendix G: Answering Difficult Questions
-Unit 6 Appendix H: Scientific Humility and Professional Language</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Audience question cards
-Mock Q&amp;A rotation schedule</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Prepares students for showcase questions and defense of evidence.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Final Reflection and Research Portfolio</x:t>
@@ -1799,7 +1701,7 @@
     <x:col min="10" max="26" width="8.630000114440918" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="4" t="s">
         <x:v>6</x:v>
       </x:c>
@@ -1828,7 +1730,7 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A2" s="5">
         <x:v>1.0</x:v>
       </x:c>
@@ -1838,41 +1740,41 @@
       <x:c r="C2" s="5" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D2" s="5" t="s">
+      <x:c r="D2" s="8" t="str">
+        <x:v>Unit 1 / Week 1</x:v>
+      </x:c>
+      <x:c r="E2" s="8" t="str"/>
+      <x:c r="F2" s="8" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5" t="s">
+      <x:c r="G2" s="8" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G2" s="5" t="s">
+      <x:c r="H2" s="8" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H2" s="5" t="s">
+      <x:c r="I2" s="8" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I2" s="5" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
+    </x:row>
+    <x:row r="3" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A3" s="5">
         <x:v>2.0</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C3" s="5" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D3" s="5" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E3" s="5"/>
-      <x:c r="F3" s="5" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G3" s="5" t="str">
+      <x:c r="D3" s="8" t="str">
+        <x:v>Unit 1 / Week 2</x:v>
+      </x:c>
+      <x:c r="E3" s="8" t="str"/>
+      <x:c r="F3" s="8" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G3" s="8" t="str">
         <x:v>Unit 1 Student Handout 3: Research Interest Inventory
 Unit 1 Student Handout 6: From Topic to Research Question
 Unit 1 Student Handout 7: Question Quality Test
@@ -1880,12 +1782,12 @@
 Unit 1 Appendix E: Strong vs. Weak Research Questions
 Unit 1 Appendix G: Engineering Design Problem Guide</x:v>
       </x:c>
-      <x:c r="H3" s="5" t="str">
+      <x:c r="H3" s="8" t="str">
         <x:v>Unit 1 Appendix I: Optional Project Card Sorting Activity
 Sticky notes or index cards</x:v>
       </x:c>
-      <x:c r="I3" s="5" t="s">
-        <x:v>25</x:v>
+      <x:c r="I3" s="8" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="132" hidden="0" customHeight="1">
@@ -1893,10 +1795,10 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
         <x:v>Unit 1 / Week 1</x:v>
@@ -1905,7 +1807,7 @@
         <x:v>Unit 2 / Week 4</x:v>
       </x:c>
       <x:c r="F4" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G4" s="8" t="str">
         <x:v>Week 1 required:
@@ -1929,10 +1831,10 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D5" s="8" t="str">
         <x:v>Unit 1 / Week 2</x:v>
@@ -1941,7 +1843,7 @@
         <x:v>Unit 2 / Week 3</x:v>
       </x:c>
       <x:c r="F5" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G5" s="8" t="str">
         <x:v>Week 2 required:
@@ -1967,17 +1869,17 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D6" s="8" t="str">
         <x:v>Unit 2 / Weeks 3-4</x:v>
       </x:c>
       <x:c r="E6" s="8" t="str"/>
       <x:c r="F6" s="8" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G6" s="8" t="str">
         <x:v>Week 3 required:
@@ -2002,17 +1904,17 @@
         <x:v>6.0</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D7" s="8" t="str">
         <x:v>Unit 3 / Week 5</x:v>
       </x:c>
       <x:c r="E7" s="8" t="str"/>
       <x:c r="F7" s="8" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G7" s="8" t="str">
         <x:v>Week 5 required weekly packet (shared with Deck 7):
@@ -2029,19 +1931,19 @@
         <x:v>7.0</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
         <x:v>Unit 3 / Week 5</x:v>
       </x:c>
       <x:c r="E8" s="8" t="str">
-        <x:v>Unit 3 / Weeks 6-16 as needed</x:v>
+        <x:v>Ongoing Unit 3 routine reference (not a scheduled weekly deck)</x:v>
       </x:c>
       <x:c r="F8" s="8" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G8" s="8" t="str">
         <x:v>Week 5 required weekly packet (shared with Deck 6):
@@ -2063,19 +1965,19 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str">
         <x:v>Unit 3 / Week 6</x:v>
       </x:c>
       <x:c r="E9" s="8" t="str">
-        <x:v>Unit 3 / Weeks 7, 10, and 13 as needed</x:v>
+        <x:v>Unit 3 / Weeks 7, 10, and 13</x:v>
       </x:c>
       <x:c r="F9" s="8" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G9" s="8" t="str">
         <x:v>Week 6 required:
@@ -2087,312 +1989,347 @@
       <x:c r="H9" s="8" t="str">
         <x:v>Week 7 revisit: Student Handouts 6-7; Appendices F-G
 Week 10 revisit: Student Handouts 11-12; Appendices K-L are optional / teacher reference
-Week 13 recovery use: Student Handout 15; Appendix P is optional / teacher reference</x:v>
+Week 13 revisit: Student Handouts 9 and 15; Appendix P is optional / teacher reference</x:v>
       </x:c>
       <x:c r="I9" s="8" t="str">
         <x:v>Use whenever a project stalls, pivots, or needs structured revision. Later-week resources remain in their assigned weekly packets.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="10" ht="184.8000030517578" hidden="0" customHeight="1">
       <x:c r="A10" s="5">
         <x:v>9.0</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
         <x:v>Unit 3 / Week 15; Unit 4 / Week 17</x:v>
       </x:c>
       <x:c r="E10" s="8" t="str">
-        <x:v>Unit 3 / Week 16 revisit</x:v>
+        <x:v>Unit 3 / Weeks 9 and 16</x:v>
       </x:c>
       <x:c r="F10" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G10" s="8" t="str">
-        <x:v>Week 15 required:
+        <x:v>Week 9 revisit required:
+Unit 3 Student Handouts 9-10
+Week 15 required:
 Unit 3 Student Handout 17: Data Audit and Organization Checklist
 Unit 3 Appendices Q-R
-Week 16 required (Deck 9 revisit):
-Unit 3 Student Handout 18: Unit 3 Readiness for Analysis Review
-Unit 3 Student Handout 19: Research Journal Self-Assessment
+Week 16 revisit required:
+Unit 3 Student Handouts 18-19
 Week 17 required:
 Unit 4 Student Handouts 1-4
 Unit 4 Appendices A-C</x:v>
       </x:c>
       <x:c r="H10" s="8" t="str">
-        <x:v>Week 16 optional / teacher reference:
+        <x:v>Week 9 optional / teacher reference:
+Unit 3 Appendix J
+Week 16 optional / teacher reference:
 Unit 3 Appendices S-U</x:v>
       </x:c>
       <x:c r="I10" s="8" t="str">
-        <x:v>Use as the Week 15 data-organization bridge, revisit in Week 16 for readiness, and teach again at the Unit 4 launch.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
+        <x:v>Reference selected concepts in Week 9, teach the deck in Week 15, revisit it in Week 16, and teach it again at the Unit 4 launch in Week 17.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A11" s="5">
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="B11" s="5" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C11" s="5" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="str">
+        <x:v>Unit 4 / Weeks 17-18</x:v>
+      </x:c>
+      <x:c r="E11" s="8" t="str"/>
+      <x:c r="F11" s="8" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C11" s="5" t="s">
+      <x:c r="G11" s="8" t="str">
+        <x:v>Week 17 required (shared with Deck 9):
+Unit 4 Student Handouts 1-4
+Unit 4 Appendices A-C
+Week 18 required:
+Unit 4 Student Handouts 5-8
+Unit 4 Appendices D-G</x:v>
+      </x:c>
+      <x:c r="H11" s="8" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D11" s="5" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E11" s="5"/>
-      <x:c r="F11" s="5" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G11" s="5" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H11" s="5" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="I11" s="5" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
+      <x:c r="I11" s="8" t="str">
+        <x:v>Introduce the analysis-selection process in Week 17 after data organization, then continue the primary instruction in Week 18.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A12" s="5">
         <x:v>11.0</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C12" s="5" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D12" s="5" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E12" s="5"/>
-      <x:c r="F12" s="5" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G12" s="5" t="str">
-        <x:v>Unit 4 Student Handout 9: Graph and Visual Selection Tool
-Unit 4 Student Handout 10: Graph Construction Checklist
-Unit 4 Student Handout 11: Error, Uncertainty, and Limitations Review
-Unit 4 Student Handout 12: Figure Caption Drafting
-Unit 4 Appendices H-K</x:v>
-      </x:c>
-      <x:c r="H12" s="5" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="I12" s="5" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
+      <x:c r="D12" s="8" t="str">
+        <x:v>Unit 4 / Week 19</x:v>
+      </x:c>
+      <x:c r="E12" s="8" t="str">
+        <x:v>Unit 5 / Week 24</x:v>
+      </x:c>
+      <x:c r="F12" s="8" t="str">
+        <x:v>Unit 4; Unit 5</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="str">
+        <x:v>Week 19 required:
+Unit 4 Student Handouts 9-12
+Unit 4 Appendices H-K
+Week 24 revisit required:
+Unit 5 Student Handout 5: Results and Visuals Builder
+Unit 5 Appendix F: Graphing Standards
+Unit 5 Appendix G: Figure and Table Caption Guide</x:v>
+      </x:c>
+      <x:c r="H12" s="8" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I12" s="8" t="str">
+        <x:v>Teach graphing and visual ethics in Week 19; revisit the visual standards during Week 24 results writing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A13" s="5">
         <x:v>12.0</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C13" s="5" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D13" s="5" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E13" s="5" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F13" s="5" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G13" s="5" t="str">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D13" s="8" t="str">
+        <x:v>Unit 4 / Week 19</x:v>
+      </x:c>
+      <x:c r="E13" s="8" t="str">
+        <x:v>Unit 4 / Week 20</x:v>
+      </x:c>
+      <x:c r="F13" s="8" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G13" s="8" t="str">
         <x:v>Unit 4 Student Handout 11: Error, Uncertainty, and Limitations Review
 Unit 4 Student Handouts 13-17
 Unit 4 Appendices J and N</x:v>
       </x:c>
-      <x:c r="H13" s="5" t="str">
+      <x:c r="H13" s="8" t="str">
         <x:v>Unit 4 Appendices L-M and O-Q (teacher reference)
 Project-specific uncertainty examples</x:v>
       </x:c>
-      <x:c r="I13" s="5" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
+      <x:c r="I13" s="8" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="198" hidden="0" customHeight="1">
       <x:c r="A14" s="5">
         <x:v>13.0</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C14" s="5" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D14" s="5" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E14" s="5"/>
-      <x:c r="F14" s="5" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G14" s="5" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H14" s="5" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="I14" s="5" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="str">
+        <x:v>Unit 5 / Week 21</x:v>
+      </x:c>
+      <x:c r="E14" s="8" t="str">
+        <x:v>Unit 5 / Weeks 22, 23, and 26</x:v>
+      </x:c>
+      <x:c r="F14" s="8" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="str">
+        <x:v>Week 21 required:
+Unit 5 Student Handouts 1-2
+Unit 5 Appendices A and L
+Week 22 revisit required:
+Unit 5 Student Handout 3
+Unit 5 Appendices B-C
+Week 23 revisit required:
+Unit 5 Student Handout 4
+Unit 5 Appendices D-E
+Week 26 revisit required:
+Unit 5 Student Handout 7
+Unit 5 Appendices J-L</x:v>
+      </x:c>
+      <x:c r="H14" s="8" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I14" s="8" t="str">
+        <x:v>Teach report architecture in Week 21; revisit the relevant report-section structure in Weeks 22, 23, and 26.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A15" s="5">
         <x:v>14.0</x:v>
       </x:c>
       <x:c r="B15" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C15" s="5" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D15" s="5" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E15" s="5" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F15" s="5" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G15" s="5" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H15" s="5" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="I15" s="5" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D15" s="8" t="str">
+        <x:v>Unit 5 / Week 25</x:v>
+      </x:c>
+      <x:c r="E15" s="8" t="str"/>
+      <x:c r="F15" s="8" t="str">
+        <x:v>Unit 5</x:v>
+      </x:c>
+      <x:c r="G15" s="8" t="str">
+        <x:v>Unit 5 Student Handout 6: Discussion Builder
+Unit 5 Appendix H: Claim-Evidence-Reasoning Guide
+Unit 5 Appendix I: Limitations and Error Analysis Guide</x:v>
+      </x:c>
+      <x:c r="H15" s="8" t="str">
+        <x:v>Student graphs, analysis summaries, and limitation notes</x:v>
+      </x:c>
+      <x:c r="I15" s="8" t="str">
+        <x:v>Primary discussion-writing deck for Week 25. Unit 4 interpretation materials are prerequisites, not a separate Week 20 deck assignment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A16" s="5">
         <x:v>15.0</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C16" s="5" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D16" s="5" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="E16" s="5"/>
-      <x:c r="F16" s="5" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G16" s="5" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H16" s="5" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="I16" s="5" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D16" s="8" t="str">
+        <x:v>Unit 5 / Week 27</x:v>
+      </x:c>
+      <x:c r="E16" s="8" t="str"/>
+      <x:c r="F16" s="8" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G16" s="8" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H16" s="8" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="I16" s="8" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="66" hidden="0" customHeight="1">
       <x:c r="A17" s="5">
         <x:v>16.0</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>81</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C17" s="5" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D17" s="5" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E17" s="5" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F17" s="5" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G17" s="5" t="str">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D17" s="8" t="str">
+        <x:v>Unit 5 / Week 28</x:v>
+      </x:c>
+      <x:c r="E17" s="8" t="str">
+        <x:v>Unit 6 / Week 32</x:v>
+      </x:c>
+      <x:c r="F17" s="8" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G17" s="8" t="str">
         <x:v>Unit 5 Student Handout 10: Presentation Planning Guide
 Unit 5 Student Handout 11: Practice Presentation Feedback Form
 Unit 5 Appendix O: Presentation Design Standards
 Unit 6 Student Handouts 10-12</x:v>
       </x:c>
-      <x:c r="H17" s="5" t="str">
+      <x:c r="H17" s="8" t="str">
         <x:v>Unit 5 Appendix Q: Practice Question Bank
 Unit 6 Appendices I-K (teacher event references)</x:v>
       </x:c>
-      <x:c r="I17" s="5" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
+      <x:c r="I17" s="8" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A18" s="5">
         <x:v>17.0</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C18" s="5" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D18" s="5" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E18" s="5" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F18" s="5" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G18" s="5" t="str">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D18" s="8" t="str">
+        <x:v>Unit 6 / Week 29</x:v>
+      </x:c>
+      <x:c r="E18" s="8" t="str">
+        <x:v>Unit 5 / Week 28 preview; Unit 6 / Week 30 revisit</x:v>
+      </x:c>
+      <x:c r="F18" s="8" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G18" s="8" t="str">
         <x:v>Unit 5 Student Handouts 10-11
 Unit 6 Student Handouts 1-6
 Unit 6 Appendices A-E</x:v>
       </x:c>
-      <x:c r="H18" s="5" t="str">
+      <x:c r="H18" s="8" t="str">
         <x:v>Unit 6 Appendix L: final summative Oral Presentation rubric (teacher scoring reference)</x:v>
       </x:c>
-      <x:c r="I18" s="5" t="s">
-        <x:v>90</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
+      <x:c r="I18" s="8" t="str">
+        <x:v>Preview spoken-presentation expectations in Week 28, teach the full deck in Week 29, and revisit it during Week 30 practice.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A19" s="5">
         <x:v>18.0</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C19" s="5" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D19" s="5" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="E19" s="5"/>
-      <x:c r="F19" s="5" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G19" s="5" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H19" s="5" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="I19" s="5" t="s">
-        <x:v>97</x:v>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D19" s="8" t="str">
+        <x:v>Unit 6 / Week 31</x:v>
+      </x:c>
+      <x:c r="E19" s="8" t="str">
+        <x:v>Unit 6 / Week 32</x:v>
+      </x:c>
+      <x:c r="F19" s="8" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G19" s="8" t="str">
+        <x:v>Week 31 required:
+Unit 6 Student Handouts 7-9
+Unit 6 Appendices F-H
+Week 32 revisit required:
+Unit 6 Student Handouts 10-12</x:v>
+      </x:c>
+      <x:c r="H19" s="8" t="str">
+        <x:v>Week 31 optional:
+Audience question cards
+Mock Q&amp;A rotation schedule
+Week 32 optional / teacher reference:
+Unit 6 Appendices I-K</x:v>
+      </x:c>
+      <x:c r="I19" s="8" t="str">
+        <x:v>Teach Q&amp;A and evidence defense in Week 31; revisit selected slides during the final Week 32 rehearsal.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="52.79999923706055" hidden="0" customHeight="1">
@@ -2400,17 +2337,17 @@
         <x:v>19.0</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>98</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C20" s="5" t="s">
-        <x:v>99</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D20" s="8" t="str">
         <x:v>Unit 6 / Week 34</x:v>
       </x:c>
       <x:c r="E20" s="8" t="str"/>
       <x:c r="F20" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G20" s="8" t="str">
         <x:v>Unit 6 Student Handout 15: Final Research Process Reflection
@@ -3423,15 +3360,15 @@
     <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="4" t="str">
         <x:v>Week</x:v>
       </x:c>
       <x:c r="B1" s="4" t="str">
         <x:v>Unit</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="str">
-        <x:v>Primary Deck(s)</x:v>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Deck Use</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
         <x:v>Required Student Copies</x:v>
@@ -3443,15 +3380,15 @@
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
         <x:v>Unit 1</x:v>
       </x:c>
-      <x:c r="C2" s="5" t="str">
-        <x:v>Decks 1, 3</x:v>
+      <x:c r="C2" s="8" t="str">
+        <x:v>Primary - Deck 1: Authentic Research Course Launch; Deck 3: Research Ethics, Safety, and Integrity</x:v>
       </x:c>
       <x:c r="D2" s="8" t="str">
         <x:v>U1 H1; U1 H2; U1 H3; U1 H4; U1 App A; U1 App B; U1 App C</x:v>
@@ -3461,15 +3398,15 @@
         <x:v>Launch course culture, research identity, ethics/integrity.</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
         <x:v>Unit 1</x:v>
       </x:c>
-      <x:c r="C3" s="5" t="str">
-        <x:v>Decks 2, 4</x:v>
+      <x:c r="C3" s="8" t="str">
+        <x:v>Primary - Deck 2: From Topic to Research Question; Deck 4: Experimental &amp; Engineering Design</x:v>
       </x:c>
       <x:c r="D3" s="8" t="str">
         <x:v>U1 H5; U1 H6; U1 H7; U1 H8; U1 App D; U1 App E; U1 App F; U1 App G; U1 App H</x:v>
@@ -3481,15 +3418,15 @@
         <x:v>Move from interests to preliminary project direction.</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="66" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
         <x:v>Unit 2</x:v>
       </x:c>
-      <x:c r="C4" s="5" t="str">
-        <x:v>Deck 5</x:v>
+      <x:c r="C4" s="8" t="str">
+        <x:v>Primary - Deck 5: Building a Formal Research Plan; Revisit / Reference - Deck 4: Experimental &amp; Engineering Design</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
         <x:v>U2 H1; U2 H2; U2 H3; U2 H4; U2 H5; U2 App A; U2 App B; U2 App C; U2 App D</x:v>
@@ -3499,15 +3436,15 @@
         <x:v>Refine question, background, hypothesis/design criteria, evidence.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="34" customHeight="1">
+    <x:row r="5" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
         <x:v>Unit 2</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="str">
-        <x:v>Deck 5</x:v>
+      <x:c r="C5" s="8" t="str">
+        <x:v>Primary - Deck 5: Building a Formal Research Plan; Revisit / Reference - Deck 3: Research Ethics, Safety, and Integrity</x:v>
       </x:c>
       <x:c r="D5" s="8" t="str">
         <x:v>U2 H6; U2 H7; U2 H8; U2 H9; U2 H10; U2 H11; U2 H12; U2 H13; U2 App E; U2 App F; U2 App G; U2 App H</x:v>
@@ -3519,15 +3456,15 @@
         <x:v>Formal research plan, safety, ethics, approval conference.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
         <x:v>Unit 3</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="str">
-        <x:v>Decks 6, 7</x:v>
+      <x:c r="C6" s="8" t="str">
+        <x:v>Primary - Deck 6: Pilot Testing; Deck 7: Research Journals and Documentation</x:v>
       </x:c>
       <x:c r="D6" s="8" t="str">
         <x:v>U3 H1; U3 H2; U3 H3; U3 App A; U3 App B; U3 App C</x:v>
@@ -3537,15 +3474,15 @@
         <x:v>Pilot test plan, journal setup, first entries.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A7" s="5" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
         <x:v>Unit 3</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="str">
-        <x:v>Deck 8</x:v>
+      <x:c r="C7" s="8" t="str">
+        <x:v>Primary - Deck 8: Troubleshooting and Responsible Project Pivots</x:v>
       </x:c>
       <x:c r="D7" s="8" t="str">
         <x:v>U3 H4; U3 H5; U3 App D; U3 App E</x:v>
@@ -3555,15 +3492,15 @@
         <x:v>Pilot reflection and troubleshooting.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A8" s="5" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
         <x:v>Unit 3</x:v>
       </x:c>
-      <x:c r="C8" s="5" t="str">
-        <x:v>Deck 8 reference</x:v>
+      <x:c r="C8" s="8" t="str">
+        <x:v>No New Deck; Revisit / Reference - Deck 8</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
         <x:v>U3 H6; U3 H7; U3 App F; U3 App G</x:v>
@@ -3573,15 +3510,15 @@
         <x:v>Revised procedure and data table audit.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A9" s="5" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
         <x:v>Unit 3</x:v>
       </x:c>
-      <x:c r="C9" s="5" t="str">
-        <x:v>Work sessions</x:v>
+      <x:c r="C9" s="8" t="str">
+        <x:v>No New Deck - systematic data collection work sessions</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str">
         <x:v>U3 H8; U3 H9; U3 App H</x:v>
@@ -3593,15 +3530,15 @@
         <x:v>Formal data collection and first data checkpoint.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A10" s="5" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
         <x:v>Unit 3</x:v>
       </x:c>
-      <x:c r="C10" s="5" t="str">
-        <x:v>Deck 9 reference</x:v>
+      <x:c r="C10" s="8" t="str">
+        <x:v>No New Deck; Revisit / Reference - Deck 9 as needed</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
         <x:v>U3 H9; U3 H10</x:v>
@@ -3613,15 +3550,15 @@
         <x:v>Data quality review.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="5" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
         <x:v>Unit 3</x:v>
       </x:c>
-      <x:c r="C11" s="5" t="str">
-        <x:v>Deck 8 reference</x:v>
+      <x:c r="C11" s="8" t="str">
+        <x:v>No New Deck; Revisit / Reference - Deck 8</x:v>
       </x:c>
       <x:c r="D11" s="8" t="str">
         <x:v>U3 H11; U3 H12</x:v>
@@ -3633,15 +3570,15 @@
         <x:v>Troubleshooting conference and mentor feedback.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A12" s="5" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="5" t="str">
         <x:v>Unit 3</x:v>
       </x:c>
-      <x:c r="C12" s="5" t="str">
-        <x:v>Work sessions</x:v>
+      <x:c r="C12" s="8" t="str">
+        <x:v>No New Deck - data collection and reliability work sessions</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
         <x:v>U3 H9; U3 H13</x:v>
@@ -3653,15 +3590,15 @@
         <x:v>Reliability and completeness check.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
+    <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A13" s="5" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
         <x:v>Unit 3</x:v>
       </x:c>
-      <x:c r="C13" s="5" t="str">
-        <x:v>Work sessions</x:v>
+      <x:c r="C13" s="8" t="str">
+        <x:v>No New Deck - midpoint review and progress reporting</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
         <x:v>U3 H14; U3 App N</x:v>
@@ -3673,15 +3610,15 @@
         <x:v>Mid-project progress report.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A14" s="5" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
         <x:v>Unit 3</x:v>
       </x:c>
-      <x:c r="C14" s="5" t="str">
-        <x:v>Work sessions</x:v>
+      <x:c r="C14" s="8" t="str">
+        <x:v>No New Deck; Revisit / Reference - Deck 8 as needed</x:v>
       </x:c>
       <x:c r="D14" s="8" t="str">
         <x:v>U3 H9; U3 H15</x:v>
@@ -3693,15 +3630,15 @@
         <x:v>Post-progress action plan.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A15" s="5" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
         <x:v>Unit 3</x:v>
       </x:c>
-      <x:c r="C15" s="5" t="str">
-        <x:v>Work sessions</x:v>
+      <x:c r="C15" s="8" t="str">
+        <x:v>No New Deck - major trial or prototype completion work sessions</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
         <x:v>U3 H9; U3 H16</x:v>
@@ -3711,15 +3648,15 @@
         <x:v>Major data collection completion check.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A16" s="5" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
         <x:v>Unit 3</x:v>
       </x:c>
-      <x:c r="C16" s="5" t="str">
-        <x:v>Deck 9</x:v>
+      <x:c r="C16" s="8" t="str">
+        <x:v>Primary - Deck 9: Data Organization, Raw vs. Clean Data</x:v>
       </x:c>
       <x:c r="D16" s="8" t="str">
         <x:v>U3 H17; U3 App Q; U3 App R</x:v>
@@ -3729,15 +3666,15 @@
         <x:v>Data audit and missing-data plan.</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A17" s="5" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
         <x:v>Unit 3</x:v>
       </x:c>
-      <x:c r="C17" s="5" t="str">
-        <x:v>Deck 9 reference</x:v>
+      <x:c r="C17" s="8" t="str">
+        <x:v>No New Deck; Revisit / Reference - Deck 9</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
         <x:v>U3 H18; U3 H19</x:v>
@@ -3749,15 +3686,15 @@
         <x:v>Readiness for Unit 4 analysis.</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A18" s="5" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
         <x:v>Unit 4</x:v>
       </x:c>
-      <x:c r="C18" s="5" t="str">
-        <x:v>Decks 9, 10</x:v>
+      <x:c r="C18" s="8" t="str">
+        <x:v>Primary - Deck 9: Data Organization; Deck 10: Choosing the Right Analysis Method</x:v>
       </x:c>
       <x:c r="D18" s="8" t="str">
         <x:v>U4 H1; U4 H2; U4 H3; U4 H4; U4 App A; U4 App B; U4 App C</x:v>
@@ -3767,15 +3704,15 @@
         <x:v>Raw data inventory, clean data set, cleaning log, audit.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A19" s="5" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
         <x:v>Unit 4</x:v>
       </x:c>
-      <x:c r="C19" s="5" t="str">
-        <x:v>Deck 10</x:v>
+      <x:c r="C19" s="8" t="str">
+        <x:v>Primary - Deck 10: Choosing the Right Analysis Method</x:v>
       </x:c>
       <x:c r="D19" s="8" t="str">
         <x:v>U4 H5; U4 H6; U4 H7; U4 H8; U4 App D; U4 App E; U4 App F; U4 App G</x:v>
@@ -3785,15 +3722,15 @@
         <x:v>Analysis method selection and calculations.</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
+    <x:row r="20" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A20" s="5" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="5" t="str">
         <x:v>Unit 4</x:v>
       </x:c>
-      <x:c r="C20" s="5" t="str">
-        <x:v>Decks 11, 12</x:v>
+      <x:c r="C20" s="8" t="str">
+        <x:v>Primary - Deck 11: Graphing and Visual Ethics; Deck 12: Error, Uncertainty, and Limitations</x:v>
       </x:c>
       <x:c r="D20" s="8" t="str">
         <x:v>U4 H9; U4 H10; U4 H11; U4 H12; U4 App H; U4 App I; U4 App J; U4 App K</x:v>
@@ -3803,15 +3740,15 @@
         <x:v>Visuals, graphing, captions, error/uncertainty.</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="34" customHeight="1">
+    <x:row r="21" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A21" s="5" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="5" t="str">
         <x:v>Unit 4</x:v>
       </x:c>
-      <x:c r="C21" s="5" t="str">
-        <x:v>Deck 12 reference</x:v>
+      <x:c r="C21" s="8" t="str">
+        <x:v>No New Deck; Revisit / Reference - Deck 12</x:v>
       </x:c>
       <x:c r="D21" s="8" t="str">
         <x:v>U4 H13; U4 H14; U4 H15; U4 H16; U4 H17; U4 App N</x:v>
@@ -3823,15 +3760,15 @@
         <x:v>Interpretation, CER, Unit 5 readiness.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="34" customHeight="1">
+    <x:row r="22" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A22" s="5" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="5" t="str">
         <x:v>Unit 5</x:v>
       </x:c>
-      <x:c r="C22" s="5" t="str">
-        <x:v>Deck 13</x:v>
+      <x:c r="C22" s="8" t="str">
+        <x:v>Primary - Deck 13: Scientific Report Structure</x:v>
       </x:c>
       <x:c r="D22" s="8" t="str">
         <x:v>U5 H1; U5 H2; U5 App A; U5 App L</x:v>
@@ -3841,15 +3778,15 @@
         <x:v>Begin public showcase planning: confirm format, target date, audience, and space.</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="15.75" customHeight="1">
+    <x:row r="23" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A23" s="5" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="5" t="str">
         <x:v>Unit 5</x:v>
       </x:c>
-      <x:c r="C23" s="5" t="str">
-        <x:v>Deck 13 reference</x:v>
+      <x:c r="C23" s="8" t="str">
+        <x:v>No New Deck; Revisit / Reference - Deck 13</x:v>
       </x:c>
       <x:c r="D23" s="8" t="str">
         <x:v>U5 H3; U5 App B; U5 App C</x:v>
@@ -3859,15 +3796,15 @@
         <x:v>Introduction writing.</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="15.75" customHeight="1">
+    <x:row r="24" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A24" s="5" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="5" t="str">
         <x:v>Unit 5</x:v>
       </x:c>
-      <x:c r="C24" s="5" t="str">
-        <x:v>Deck 13 reference</x:v>
+      <x:c r="C24" s="8" t="str">
+        <x:v>No New Deck; Revisit / Reference - Deck 13</x:v>
       </x:c>
       <x:c r="D24" s="8" t="str">
         <x:v>U5 H4; U5 App D; U5 App E</x:v>
@@ -3877,15 +3814,15 @@
         <x:v>Methods writing.</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="34" customHeight="1">
+    <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A25" s="5" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
         <x:v>Unit 5</x:v>
       </x:c>
-      <x:c r="C25" s="5" t="str">
-        <x:v>Deck 11 reference</x:v>
+      <x:c r="C25" s="8" t="str">
+        <x:v>No New Deck; Revisit / Reference - Deck 11</x:v>
       </x:c>
       <x:c r="D25" s="8" t="str">
         <x:v>U5 H5; U5 App F; U5 App G</x:v>
@@ -3895,15 +3832,15 @@
         <x:v>Results and visuals; send invitations or confirm the public audience.</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="15.75" customHeight="1">
+    <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A26" s="5" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="5" t="str">
         <x:v>Unit 5</x:v>
       </x:c>
-      <x:c r="C26" s="5" t="str">
-        <x:v>Deck 14</x:v>
+      <x:c r="C26" s="8" t="str">
+        <x:v>Primary - Deck 14: Writing the Discussion with CER</x:v>
       </x:c>
       <x:c r="D26" s="8" t="str">
         <x:v>U5 H6; U5 App H; U5 App I</x:v>
@@ -3913,15 +3850,15 @@
         <x:v>Discussion and CER.</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="15.75" customHeight="1">
+    <x:row r="27" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A27" s="5" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="5" t="str">
         <x:v>Unit 5</x:v>
       </x:c>
-      <x:c r="C27" s="5" t="str">
-        <x:v>Deck 13 reference</x:v>
+      <x:c r="C27" s="8" t="str">
+        <x:v>No New Deck; Revisit / Reference - Deck 13</x:v>
       </x:c>
       <x:c r="D27" s="8" t="str">
         <x:v>U5 H7; U5 App J; U5 App K; U5 App L</x:v>
@@ -3931,15 +3868,15 @@
         <x:v>Conclusion and full draft assembly.</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="34" customHeight="1">
+    <x:row r="28" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A28" s="5" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="5" t="str">
         <x:v>Unit 5</x:v>
       </x:c>
-      <x:c r="C28" s="5" t="str">
-        <x:v>Deck 15</x:v>
+      <x:c r="C28" s="8" t="str">
+        <x:v>Primary - Deck 15: Peer Review and Scientific Revision</x:v>
       </x:c>
       <x:c r="D28" s="8" t="str">
         <x:v>U5 H8; U5 H9; U5 App M; U5 App N</x:v>
@@ -3949,15 +3886,15 @@
         <x:v>Peer review; finalize event logistics, technology, accessibility, and assessment workflow.</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="15.75" customHeight="1">
+    <x:row r="29" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A29" s="5" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="5" t="str">
         <x:v>Unit 5</x:v>
       </x:c>
-      <x:c r="C29" s="5" t="str">
-        <x:v>Deck 16; Deck 17 preview</x:v>
+      <x:c r="C29" s="8" t="str">
+        <x:v>Primary - Deck 16: Designing a Research Poster/Board; Preview / Reference - Deck 17</x:v>
       </x:c>
       <x:c r="D29" s="8" t="str">
         <x:v>U5 H10; U5 H11; U5 App O</x:v>
@@ -3969,15 +3906,15 @@
         <x:v>Presentation design and practice.</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="15.75" customHeight="1">
+    <x:row r="30" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A30" s="5" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="5" t="str">
         <x:v>Unit 6</x:v>
       </x:c>
-      <x:c r="C30" s="5" t="str">
-        <x:v>Deck 17</x:v>
+      <x:c r="C30" s="8" t="str">
+        <x:v>Primary - Deck 17: Oral Presentation Skills for Research</x:v>
       </x:c>
       <x:c r="D30" s="8" t="str">
         <x:v>U6 H1; U6 H2; U6 H3; U6 App A; U6 App B; U6 App C</x:v>
@@ -3987,15 +3924,15 @@
         <x:v>Presentation readiness and message refinement.</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="15.75" customHeight="1">
+    <x:row r="31" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A31" s="5" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="5" t="str">
         <x:v>Unit 6</x:v>
       </x:c>
-      <x:c r="C31" s="5" t="str">
-        <x:v>Deck 17 reference</x:v>
+      <x:c r="C31" s="8" t="str">
+        <x:v>No New Deck; Revisit / Reference - Deck 17</x:v>
       </x:c>
       <x:c r="D31" s="8" t="str">
         <x:v>U6 H4; U6 H5; U6 H6; U6 App D; U6 App E</x:v>
@@ -4005,15 +3942,15 @@
         <x:v>Practice presentations and audience adaptation.</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="15.75" customHeight="1">
+    <x:row r="32" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A32" s="5" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="5" t="str">
         <x:v>Unit 6</x:v>
       </x:c>
-      <x:c r="C32" s="5" t="str">
-        <x:v>Deck 18</x:v>
+      <x:c r="C32" s="8" t="str">
+        <x:v>Primary - Deck 18: Answering Questions Like a Scientist</x:v>
       </x:c>
       <x:c r="D32" s="8" t="str">
         <x:v>U6 H7; U6 H8; U6 H9; U6 App F; U6 App G; U6 App H</x:v>
@@ -4023,15 +3960,15 @@
         <x:v>Q&amp;A preparation and evidence defense.</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="15.75" customHeight="1">
+    <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A33" s="5" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="5" t="str">
         <x:v>Unit 6</x:v>
       </x:c>
-      <x:c r="C33" s="5" t="str">
-        <x:v>Decks 16, 18 reference</x:v>
+      <x:c r="C33" s="8" t="str">
+        <x:v>No New Deck; Revisit / Reference - Decks 16 and 18</x:v>
       </x:c>
       <x:c r="D33" s="8" t="str">
         <x:v>U6 H10; U6 H11; U6 H12</x:v>
@@ -4043,15 +3980,15 @@
         <x:v>Final showcase preparation.</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="34" customHeight="1">
+    <x:row r="34" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A34" s="5" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="5" t="str">
         <x:v>Unit 6</x:v>
       </x:c>
-      <x:c r="C34" s="5" t="str">
-        <x:v>Work sessions</x:v>
+      <x:c r="C34" s="8" t="str">
+        <x:v>No New Deck - required public presentation or showcase</x:v>
       </x:c>
       <x:c r="D34" s="8" t="str">
         <x:v>U6 H13; U6 H14; U6 App L; U6 App M</x:v>
@@ -4063,15 +4000,15 @@
         <x:v>Required public presentation/showcase with a genuine public audience.</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="48" customHeight="1">
+    <x:row r="35" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A35" s="5" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="5" t="str">
         <x:v>Unit 6</x:v>
       </x:c>
-      <x:c r="C35" s="5" t="str">
-        <x:v>Deck 19</x:v>
+      <x:c r="C35" s="8" t="str">
+        <x:v>Primary - Deck 19: Final Reflection and Research Portfolio</x:v>
       </x:c>
       <x:c r="D35" s="8" t="str">
         <x:v>U6 H15; U6 H16; U6 H18</x:v>
@@ -5067,101 +5004,101 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C1" s="4" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D1" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E1" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C2" s="5" t="s">
-        <x:v>106</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D2" s="5" t="s">
-        <x:v>107</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E2" s="5" t="s">
-        <x:v>108</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>109</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
-        <x:v>110</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D3" s="5" t="s">
-        <x:v>111</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E3" s="5" t="s">
-        <x:v>112</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>113</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>114</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>115</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>116</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="5" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>117</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>118</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>119</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>120</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>121</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>122</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
         <x:v>Student Handouts 1-11; Appendixes A-O and Q-S; Unit 6 Appendix L is the final oral rubric</x:v>
@@ -5169,19 +5106,19 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="5" t="s">
-        <x:v>94</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>124</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
         <x:v>Presentation, required public showcase, Q&amp;A, reflection, portfolio, and next steps</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>125</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1"/>
@@ -6180,10 +6117,10 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -6191,7 +6128,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>129</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6199,7 +6136,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>130</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -6207,7 +6144,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>131</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6215,7 +6152,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>132</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6223,7 +6160,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>133</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -6236,18 +6173,18 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="s">
-        <x:v>134</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>135</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="5" t="s">
-        <x:v>136</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>137</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="10">

--- a/Teacher Resources (Start Here)/06_STARLAB_Master_Print_Packet_Index.xlsx
+++ b/Teacher Resources (Start Here)/06_STARLAB_Master_Print_Packet_Index.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R2730892ae6044289"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print Packet Index" sheetId="2" r:id="R7f7fed98e2d24fc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Print Queue" sheetId="3" r:id="Ra6dbc8079c654db8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Unit" sheetId="4" r:id="R500c174791e84cff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Type Key" sheetId="5" r:id="Rcf33a24bc93742ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R37d9d0116a334240"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print Packet Index" sheetId="2" r:id="Rb13766931e3f4f9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Print Queue" sheetId="3" r:id="R28019e65321e4255"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Unit" sheetId="4" r:id="Rb8808cd605f04a7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Type Key" sheetId="5" r:id="Ra35ac0bbfa71454d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -173,9 +173,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Deck 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Use after initial graphs/calculations; revisit before interpretation.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Scientific Report Structure</x:t>
@@ -2103,7 +2100,7 @@
         <x:v>Teach graphing and visual ethics in Week 19; revisit the visual standards during Week 24 results writing.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="52.79999923706055" hidden="0" customHeight="1">
+    <x:row r="13" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A13" s="5">
         <x:v>12.0</x:v>
       </x:c>
@@ -2123,16 +2120,20 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="G13" s="8" t="str">
-        <x:v>Unit 4 Student Handout 11: Error, Uncertainty, and Limitations Review
+        <x:v>Week 19 required:
+Unit 4 Student Handouts 9-12
+Unit 4 Appendices H-K
+Week 20 revisit required:
 Unit 4 Student Handouts 13-17
-Unit 4 Appendices J and N</x:v>
+Unit 4 Appendix N</x:v>
       </x:c>
       <x:c r="H13" s="8" t="str">
-        <x:v>Unit 4 Appendices L-M and O-Q (teacher reference)
+        <x:v>Week 20 optional / teacher reference:
+Unit 4 Appendices L-M and O-Q
 Project-specific uncertainty examples</x:v>
       </x:c>
-      <x:c r="I13" s="8" t="s">
-        <x:v>51</x:v>
+      <x:c r="I13" s="8" t="str">
+        <x:v>Teach error, uncertainty, variability, and limitations in Week 19; revisit the relevant ideas before students finalize interpretation and claims in Week 20.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="198" hidden="0" customHeight="1">
@@ -2140,10 +2141,10 @@
         <x:v>13.0</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C14" s="5" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="C14" s="5" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="D14" s="8" t="str">
         <x:v>Unit 5 / Week 21</x:v>
@@ -2152,7 +2153,7 @@
         <x:v>Unit 5 / Weeks 22, 23, and 26</x:v>
       </x:c>
       <x:c r="F14" s="8" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G14" s="8" t="str">
         <x:v>Week 21 required:
@@ -2169,7 +2170,7 @@
 Unit 5 Appendices J-L</x:v>
       </x:c>
       <x:c r="H14" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I14" s="8" t="str">
         <x:v>Teach report architecture in Week 21; revisit the relevant report-section structure in Weeks 22, 23, and 26.</x:v>
@@ -2180,10 +2181,10 @@
         <x:v>14.0</x:v>
       </x:c>
       <x:c r="B15" s="5" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C15" s="5" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="C15" s="5" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
         <x:v>Unit 5 / Week 25</x:v>
@@ -2209,26 +2210,26 @@
         <x:v>15.0</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C16" s="5" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="C16" s="5" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="D16" s="8" t="str">
         <x:v>Unit 5 / Week 27</x:v>
       </x:c>
       <x:c r="E16" s="8" t="str"/>
       <x:c r="F16" s="8" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G16" s="8" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H16" s="8" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="H16" s="8" t="s">
+      <x:c r="I16" s="8" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="I16" s="8" t="s">
-        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="66" hidden="0" customHeight="1">
@@ -2236,10 +2237,10 @@
         <x:v>16.0</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C17" s="5" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="C17" s="5" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
         <x:v>Unit 5 / Week 28</x:v>
@@ -2248,7 +2249,7 @@
         <x:v>Unit 6 / Week 32</x:v>
       </x:c>
       <x:c r="F17" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G17" s="8" t="str">
         <x:v>Unit 5 Student Handout 10: Presentation Planning Guide
@@ -2261,7 +2262,7 @@
 Unit 6 Appendices I-K (teacher event references)</x:v>
       </x:c>
       <x:c r="I17" s="8" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -2269,10 +2270,10 @@
         <x:v>17.0</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C18" s="5" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="C18" s="5" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="D18" s="8" t="str">
         <x:v>Unit 6 / Week 29</x:v>
@@ -2281,7 +2282,7 @@
         <x:v>Unit 5 / Week 28 preview; Unit 6 / Week 30 revisit</x:v>
       </x:c>
       <x:c r="F18" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G18" s="8" t="str">
         <x:v>Unit 5 Student Handouts 10-11
@@ -2300,10 +2301,10 @@
         <x:v>18.0</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C19" s="5" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="C19" s="5" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="D19" s="8" t="str">
         <x:v>Unit 6 / Week 31</x:v>
@@ -2312,7 +2313,7 @@
         <x:v>Unit 6 / Week 32</x:v>
       </x:c>
       <x:c r="F19" s="8" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G19" s="8" t="str">
         <x:v>Week 31 required:
@@ -2337,17 +2338,17 @@
         <x:v>19.0</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C20" s="5" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="C20" s="5" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="D20" s="8" t="str">
         <x:v>Unit 6 / Week 34</x:v>
       </x:c>
       <x:c r="E20" s="8" t="str"/>
       <x:c r="F20" s="8" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G20" s="8" t="str">
         <x:v>Unit 6 Student Handout 15: Final Research Process Reflection
@@ -5004,19 +5005,19 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="s">
+      <x:c r="C1" s="4" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="s">
+      <x:c r="D1" s="4" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D1" s="4" t="s">
+      <x:c r="E1" s="4" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="E1" s="4" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -5024,16 +5025,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C2" s="5" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C2" s="5" t="s">
+      <x:c r="D2" s="5" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D2" s="5" t="s">
+      <x:c r="E2" s="5" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="E2" s="5" t="s">
-        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -5041,16 +5042,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="C3" s="5" t="s">
+      <x:c r="D3" s="5" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="D3" s="5" t="s">
+      <x:c r="E3" s="5" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="E3" s="5" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -5058,16 +5059,16 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C4" s="5" t="s">
+      <x:c r="D4" s="5" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D4" s="5" t="s">
+      <x:c r="E4" s="5" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="s">
-        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -5075,30 +5076,30 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="s">
+      <x:c r="D5" s="5" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="s">
+      <x:c r="E5" s="5" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="E5" s="5" t="s">
-        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="s">
+      <x:c r="D6" s="5" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
         <x:v>Student Handouts 1-11; Appendixes A-O and Q-S; Unit 6 Appendix L is the final oral rubric</x:v>
@@ -5106,19 +5107,19 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
         <x:v>Presentation, required public showcase, Q&amp;A, reflection, portfolio, and next steps</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E7" s="5" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="E7" s="5" t="s">
-        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1"/>
@@ -6117,10 +6118,10 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="4" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="B1" s="4" t="s">
-        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -6128,7 +6129,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6136,7 +6137,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -6144,7 +6145,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6152,7 +6153,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6160,7 +6161,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -6173,18 +6174,18 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="s">
-        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="5" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="10">

--- a/Teacher Resources (Start Here)/06_STARLAB_Master_Print_Packet_Index.xlsx
+++ b/Teacher Resources (Start Here)/06_STARLAB_Master_Print_Packet_Index.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R37d9d0116a334240"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print Packet Index" sheetId="2" r:id="Rb13766931e3f4f9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Print Queue" sheetId="3" r:id="R28019e65321e4255"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Unit" sheetId="4" r:id="Rb8808cd605f04a7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Type Key" sheetId="5" r:id="Ra35ac0bbfa71454d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rc75939a0b50f4161"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print Packet Index" sheetId="2" r:id="Ra6aee84c7ee744ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Print Queue" sheetId="3" r:id="Rffd4691c09f041ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Unit" sheetId="4" r:id="R1bb651d7f797403d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Type Key" sheetId="5" r:id="R7efaf8d206594452"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -76,10 +76,6 @@
 Unit 1 Appendix C: Research Fields and Topic Bank</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Course syllabus or overview
-Student onboarding packet, if available</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Introductory culture-setting deck. Deck order stays linear; the primary teaching moment is separated from any resource-folder references.</x:t>
   </x:si>
   <x:si>
@@ -182,10 +178,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Unit 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Model report or simplified published paper
-Weak sample report or teacher-created flawed example</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Writing the Discussion: Claim, Evidence, Reasoning</x:t>
@@ -1727,7 +1719,7 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="2" ht="132" hidden="0" customHeight="1">
       <x:c r="A2" s="5">
         <x:v>1.0</x:v>
       </x:c>
@@ -1747,11 +1739,16 @@
       <x:c r="G2" s="8" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H2" s="8" t="s">
+      <x:c r="H2" s="8" t="str">
+        <x:v>Course syllabus or overview
+Student onboarding packet, if available
+Week 1 optional / teacher reference:
+Unit 1 Appendix I: Optional Project Card Sorting Activity
+Unit 1 Appendix J: Optional Initial Parent or Guardian Communication
+Unit 1 Appendix L: Differentiation and Implementation Notes</x:v>
+      </x:c>
+      <x:c r="I2" s="8" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="I2" s="8" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="79.19999694824219" hidden="0" customHeight="1">
@@ -1759,10 +1756,10 @@
         <x:v>2.0</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="C3" s="5" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="D3" s="8" t="str">
         <x:v>Unit 1 / Week 2</x:v>
@@ -1781,10 +1778,12 @@
       </x:c>
       <x:c r="H3" s="8" t="str">
         <x:v>Unit 1 Appendix I: Optional Project Card Sorting Activity
-Sticky notes or index cards</x:v>
+Sticky notes or index cards
+Week 2 optional teacher reference:
+Unit 1 Appendix K: Unit 1 Teacher Checklist</x:v>
       </x:c>
       <x:c r="I3" s="8" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="132" hidden="0" customHeight="1">
@@ -1792,10 +1791,10 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
         <x:v>Unit 1 / Week 1</x:v>
@@ -1804,7 +1803,7 @@
         <x:v>Unit 2 / Week 4</x:v>
       </x:c>
       <x:c r="F4" s="8" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G4" s="8" t="str">
         <x:v>Week 1 required:
@@ -1817,7 +1816,11 @@
 Unit 2 Appendix H: Project Approval Checklist</x:v>
       </x:c>
       <x:c r="H4" s="8" t="str">
-        <x:v>District-supplied safety, human-participant, privacy, media, fieldwork, equipment, chemical, drone, IRB/SRC, or other local forms as applicable.</x:v>
+        <x:v>District-supplied safety, human-participant, privacy, media, fieldwork, equipment, chemical, drone, IRB/SRC, or other local forms as applicable.
+Additional Week 1 teacher references:
+Unit 1 Appendices J and L
+Additional Week 4 teacher reference:
+Unit 2 Appendix L: Unit 2 Teacher Checklist</x:v>
       </x:c>
       <x:c r="I4" s="8" t="str">
         <x:v>Introduce in Week 1 as course culture; revisit in Week 4 during formal project approval.</x:v>
@@ -1828,10 +1831,10 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="D5" s="8" t="str">
         <x:v>Unit 1 / Week 2</x:v>
@@ -1840,7 +1843,7 @@
         <x:v>Unit 2 / Week 3</x:v>
       </x:c>
       <x:c r="F5" s="8" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G5" s="8" t="str">
         <x:v>Week 2 required:
@@ -1855,28 +1858,31 @@
       <x:c r="H5" s="8" t="str">
         <x:v>Week 2 optional / teacher reference:
 Unit 1 Appendix I: Optional Project Card Sorting Activity
-Mini-investigation supplies</x:v>
+Mini-investigation supplies
+Additional teacher references:
+Week 2 - Unit 1 Appendix K
+Week 3 - Unit 2 Appendix K</x:v>
       </x:c>
       <x:c r="I5" s="8" t="str">
         <x:v>Use first as a Week 2 foundation lesson; revisit during Week 3 planning.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="6" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A6" s="5">
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="D6" s="8" t="str">
         <x:v>Unit 2 / Weeks 3-4</x:v>
       </x:c>
       <x:c r="E6" s="8" t="str"/>
       <x:c r="F6" s="8" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G6" s="8" t="str">
         <x:v>Week 3 required:
@@ -1890,7 +1896,10 @@
         <x:v>Week 4 optional / teacher reference:
 Unit 2 Appendix I: Mentor Feedback Request Template
 Unit 2 Appendix J: Sample Completed Planning Excerpt
-District-supplied approval and safety forms as applicable</x:v>
+District-supplied approval and safety forms as applicable
+Additional optional teacher references:
+Week 3 - Unit 2 Appendix K
+Week 4 - Unit 2 Appendix L</x:v>
       </x:c>
       <x:c r="I6" s="8" t="str">
         <x:v>The main Unit 2 planning and approval deck. The Week 3 and Week 4 packets are separated here to match the implementation calendar.</x:v>
@@ -1901,17 +1910,17 @@
         <x:v>6.0</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="D7" s="8" t="str">
         <x:v>Unit 3 / Week 5</x:v>
       </x:c>
       <x:c r="E7" s="8" t="str"/>
       <x:c r="F7" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G7" s="8" t="str">
         <x:v>Week 5 required weekly packet (shared with Deck 7):
@@ -1928,10 +1937,10 @@
         <x:v>7.0</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
         <x:v>Unit 3 / Week 5</x:v>
@@ -1940,7 +1949,7 @@
         <x:v>Ongoing Unit 3 routine reference (not a scheduled weekly deck)</x:v>
       </x:c>
       <x:c r="F8" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G8" s="8" t="str">
         <x:v>Week 5 required weekly packet (shared with Deck 6):
@@ -1962,10 +1971,10 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="C9" s="5" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str">
         <x:v>Unit 3 / Week 6</x:v>
@@ -1974,7 +1983,7 @@
         <x:v>Unit 3 / Weeks 7, 10, and 13</x:v>
       </x:c>
       <x:c r="F9" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G9" s="8" t="str">
         <x:v>Week 6 required:
@@ -1997,10 +2006,10 @@
         <x:v>9.0</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C10" s="5" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="C10" s="5" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
         <x:v>Unit 3 / Week 15; Unit 4 / Week 17</x:v>
@@ -2009,7 +2018,7 @@
         <x:v>Unit 3 / Weeks 9 and 16</x:v>
       </x:c>
       <x:c r="F10" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G10" s="8" t="str">
         <x:v>Week 9 revisit required:
@@ -2038,17 +2047,17 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="B11" s="5" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C11" s="5" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="C11" s="5" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="D11" s="8" t="str">
         <x:v>Unit 4 / Weeks 17-18</x:v>
       </x:c>
       <x:c r="E11" s="8" t="str"/>
       <x:c r="F11" s="8" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G11" s="8" t="str">
         <x:v>Week 17 required (shared with Deck 9):
@@ -2059,7 +2068,7 @@
 Unit 4 Appendices D-G</x:v>
       </x:c>
       <x:c r="H11" s="8" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I11" s="8" t="str">
         <x:v>Introduce the analysis-selection process in Week 17 after data organization, then continue the primary instruction in Week 18.</x:v>
@@ -2070,10 +2079,10 @@
         <x:v>11.0</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C12" s="5" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="C12" s="5" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
         <x:v>Unit 4 / Week 19</x:v>
@@ -2094,7 +2103,7 @@
 Unit 5 Appendix G: Figure and Table Caption Guide</x:v>
       </x:c>
       <x:c r="H12" s="8" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I12" s="8" t="str">
         <x:v>Teach graphing and visual ethics in Week 19; revisit the visual standards during Week 24 results writing.</x:v>
@@ -2105,10 +2114,10 @@
         <x:v>12.0</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C13" s="5" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="C13" s="5" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
         <x:v>Unit 4 / Week 19</x:v>
@@ -2117,7 +2126,7 @@
         <x:v>Unit 4 / Week 20</x:v>
       </x:c>
       <x:c r="F13" s="8" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G13" s="8" t="str">
         <x:v>Week 19 required:
@@ -2141,10 +2150,10 @@
         <x:v>13.0</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C14" s="5" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="C14" s="5" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="D14" s="8" t="str">
         <x:v>Unit 5 / Week 21</x:v>
@@ -2153,7 +2162,7 @@
         <x:v>Unit 5 / Weeks 22, 23, and 26</x:v>
       </x:c>
       <x:c r="F14" s="8" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G14" s="8" t="str">
         <x:v>Week 21 required:
@@ -2169,8 +2178,12 @@
 Unit 5 Student Handout 7
 Unit 5 Appendices J-L</x:v>
       </x:c>
-      <x:c r="H14" s="8" t="s">
-        <x:v>54</x:v>
+      <x:c r="H14" s="8" t="str">
+        <x:v>Model report or simplified published paper
+Weak sample report or teacher-created flawed example
+Week 21 optional teacher references:
+Unit 5 Appendix R: Teacher Implementation Notes for New STARLAB Chapters
+Unit 5 Appendix S: STARLAB Research Showcase Preparation</x:v>
       </x:c>
       <x:c r="I14" s="8" t="str">
         <x:v>Teach report architecture in Week 21; revisit the relevant report-section structure in Weeks 22, 23, and 26.</x:v>
@@ -2181,10 +2194,10 @@
         <x:v>14.0</x:v>
       </x:c>
       <x:c r="B15" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C15" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
         <x:v>Unit 5 / Week 25</x:v>
@@ -2210,26 +2223,26 @@
         <x:v>15.0</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C16" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D16" s="8" t="str">
         <x:v>Unit 5 / Week 27</x:v>
       </x:c>
       <x:c r="E16" s="8" t="str"/>
       <x:c r="F16" s="8" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G16" s="8" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H16" s="8" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I16" s="8" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="H16" s="8" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I16" s="8" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="66" hidden="0" customHeight="1">
@@ -2237,10 +2250,10 @@
         <x:v>16.0</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C17" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
         <x:v>Unit 5 / Week 28</x:v>
@@ -2249,7 +2262,7 @@
         <x:v>Unit 6 / Week 32</x:v>
       </x:c>
       <x:c r="F17" s="8" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G17" s="8" t="str">
         <x:v>Unit 5 Student Handout 10: Presentation Planning Guide
@@ -2262,7 +2275,7 @@
 Unit 6 Appendices I-K (teacher event references)</x:v>
       </x:c>
       <x:c r="I17" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -2270,10 +2283,10 @@
         <x:v>17.0</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C18" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D18" s="8" t="str">
         <x:v>Unit 6 / Week 29</x:v>
@@ -2282,7 +2295,7 @@
         <x:v>Unit 5 / Week 28 preview; Unit 6 / Week 30 revisit</x:v>
       </x:c>
       <x:c r="F18" s="8" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G18" s="8" t="str">
         <x:v>Unit 5 Student Handouts 10-11
@@ -2296,15 +2309,15 @@
         <x:v>Preview spoken-presentation expectations in Week 28, teach the full deck in Week 29, and revisit it during Week 30 practice.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="19" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A19" s="5">
         <x:v>18.0</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C19" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D19" s="8" t="str">
         <x:v>Unit 6 / Week 31</x:v>
@@ -2313,7 +2326,7 @@
         <x:v>Unit 6 / Week 32</x:v>
       </x:c>
       <x:c r="F19" s="8" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G19" s="8" t="str">
         <x:v>Week 31 required:
@@ -2327,7 +2340,9 @@
 Audience question cards
 Mock Q&amp;A rotation schedule
 Week 32 optional / teacher reference:
-Unit 6 Appendices I-K</x:v>
+Unit 6 Appendices I-K
+Weeks 31-32 optional teacher scoring reference:
+Unit 6 Appendix L: Oral Presentation Rubric</x:v>
       </x:c>
       <x:c r="I19" s="8" t="str">
         <x:v>Teach Q&amp;A and evidence defense in Week 31; revisit selected slides during the final Week 32 rehearsal.</x:v>
@@ -2338,17 +2353,17 @@
         <x:v>19.0</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C20" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D20" s="8" t="str">
         <x:v>Unit 6 / Week 34</x:v>
       </x:c>
       <x:c r="E20" s="8" t="str"/>
       <x:c r="F20" s="8" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G20" s="8" t="str">
         <x:v>Unit 6 Student Handout 15: Final Research Process Reflection
@@ -3394,7 +3409,9 @@
       <x:c r="D2" s="8" t="str">
         <x:v>U1 H1; U1 H2; U1 H3; U1 H4; U1 App A; U1 App B; U1 App C</x:v>
       </x:c>
-      <x:c r="E2" s="8" t="str"/>
+      <x:c r="E2" s="8" t="str">
+        <x:v>U1 App I; U1 App J; U1 App L</x:v>
+      </x:c>
       <x:c r="F2" s="7" t="str">
         <x:v>Launch course culture, research identity, ethics/integrity.</x:v>
       </x:c>
@@ -3413,7 +3430,7 @@
         <x:v>U1 H5; U1 H6; U1 H7; U1 H8; U1 App D; U1 App E; U1 App F; U1 App G; U1 App H</x:v>
       </x:c>
       <x:c r="E3" s="8" t="str">
-        <x:v>U1 App I</x:v>
+        <x:v>U1 App I; U1 App K</x:v>
       </x:c>
       <x:c r="F3" s="7" t="str">
         <x:v>Move from interests to preliminary project direction.</x:v>
@@ -3432,7 +3449,9 @@
       <x:c r="D4" s="8" t="str">
         <x:v>U2 H1; U2 H2; U2 H3; U2 H4; U2 H5; U2 App A; U2 App B; U2 App C; U2 App D</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str"/>
+      <x:c r="E4" s="8" t="str">
+        <x:v>U2 App K</x:v>
+      </x:c>
       <x:c r="F4" s="7" t="str">
         <x:v>Refine question, background, hypothesis/design criteria, evidence.</x:v>
       </x:c>
@@ -3451,7 +3470,7 @@
         <x:v>U2 H6; U2 H7; U2 H8; U2 H9; U2 H10; U2 H11; U2 H12; U2 H13; U2 App E; U2 App F; U2 App G; U2 App H</x:v>
       </x:c>
       <x:c r="E5" s="8" t="str">
-        <x:v>U2 AppI; U2 AppJ; district-supplied approval and safety forms as applicable</x:v>
+        <x:v>U2 App I; U2 App J; U2 App L; district-supplied approval and safety forms as applicable</x:v>
       </x:c>
       <x:c r="F5" s="7" t="str">
         <x:v>Formal research plan, safety, ethics, approval conference.</x:v>
@@ -3470,7 +3489,7 @@
       <x:c r="D6" s="8" t="str">
         <x:v>U3 H1; U3 H2; U3 H3; U3 App A; U3 App B; U3 App C</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str"/>
+      <x:c r="E6" s="8"/>
       <x:c r="F6" s="7" t="str">
         <x:v>Pilot test plan, journal setup, first entries.</x:v>
       </x:c>
@@ -3488,7 +3507,7 @@
       <x:c r="D7" s="8" t="str">
         <x:v>U3 H4; U3 H5; U3 App D; U3 App E</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str"/>
+      <x:c r="E7" s="8"/>
       <x:c r="F7" s="7" t="str">
         <x:v>Pilot reflection and troubleshooting.</x:v>
       </x:c>
@@ -3506,7 +3525,7 @@
       <x:c r="D8" s="8" t="str">
         <x:v>U3 H6; U3 H7; U3 App F; U3 App G</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="str"/>
+      <x:c r="E8" s="8"/>
       <x:c r="F8" s="7" t="str">
         <x:v>Revised procedure and data table audit.</x:v>
       </x:c>
@@ -3644,7 +3663,7 @@
       <x:c r="D15" s="8" t="str">
         <x:v>U3 H9; U3 H16</x:v>
       </x:c>
-      <x:c r="E15" s="8" t="str"/>
+      <x:c r="E15" s="8"/>
       <x:c r="F15" s="7" t="str">
         <x:v>Major data collection completion check.</x:v>
       </x:c>
@@ -3662,7 +3681,7 @@
       <x:c r="D16" s="8" t="str">
         <x:v>U3 H17; U3 App Q; U3 App R</x:v>
       </x:c>
-      <x:c r="E16" s="8" t="str"/>
+      <x:c r="E16" s="8"/>
       <x:c r="F16" s="7" t="str">
         <x:v>Data audit and missing-data plan.</x:v>
       </x:c>
@@ -3700,7 +3719,7 @@
       <x:c r="D18" s="8" t="str">
         <x:v>U4 H1; U4 H2; U4 H3; U4 H4; U4 App A; U4 App B; U4 App C</x:v>
       </x:c>
-      <x:c r="E18" s="8" t="str"/>
+      <x:c r="E18" s="8"/>
       <x:c r="F18" s="7" t="str">
         <x:v>Raw data inventory, clean data set, cleaning log, audit.</x:v>
       </x:c>
@@ -3718,7 +3737,7 @@
       <x:c r="D19" s="8" t="str">
         <x:v>U4 H5; U4 H6; U4 H7; U4 H8; U4 App D; U4 App E; U4 App F; U4 App G</x:v>
       </x:c>
-      <x:c r="E19" s="8" t="str"/>
+      <x:c r="E19" s="8"/>
       <x:c r="F19" s="7" t="str">
         <x:v>Analysis method selection and calculations.</x:v>
       </x:c>
@@ -3736,7 +3755,7 @@
       <x:c r="D20" s="8" t="str">
         <x:v>U4 H9; U4 H10; U4 H11; U4 H12; U4 App H; U4 App I; U4 App J; U4 App K</x:v>
       </x:c>
-      <x:c r="E20" s="8" t="str"/>
+      <x:c r="E20" s="8"/>
       <x:c r="F20" s="7" t="str">
         <x:v>Visuals, graphing, captions, error/uncertainty.</x:v>
       </x:c>
@@ -3774,7 +3793,9 @@
       <x:c r="D22" s="8" t="str">
         <x:v>U5 H1; U5 H2; U5 App A; U5 App L</x:v>
       </x:c>
-      <x:c r="E22" s="8" t="str"/>
+      <x:c r="E22" s="8" t="str">
+        <x:v>U5 App R; U5 App S</x:v>
+      </x:c>
       <x:c r="F22" s="7" t="str">
         <x:v>Begin public showcase planning: confirm format, target date, audience, and space.</x:v>
       </x:c>
@@ -3792,7 +3813,7 @@
       <x:c r="D23" s="8" t="str">
         <x:v>U5 H3; U5 App B; U5 App C</x:v>
       </x:c>
-      <x:c r="E23" s="8" t="str"/>
+      <x:c r="E23" s="8"/>
       <x:c r="F23" s="7" t="str">
         <x:v>Introduction writing.</x:v>
       </x:c>
@@ -3810,7 +3831,7 @@
       <x:c r="D24" s="8" t="str">
         <x:v>U5 H4; U5 App D; U5 App E</x:v>
       </x:c>
-      <x:c r="E24" s="8" t="str"/>
+      <x:c r="E24" s="8"/>
       <x:c r="F24" s="7" t="str">
         <x:v>Methods writing.</x:v>
       </x:c>
@@ -3828,7 +3849,7 @@
       <x:c r="D25" s="8" t="str">
         <x:v>U5 H5; U5 App F; U5 App G</x:v>
       </x:c>
-      <x:c r="E25" s="8" t="str"/>
+      <x:c r="E25" s="8"/>
       <x:c r="F25" s="7" t="str">
         <x:v>Results and visuals; send invitations or confirm the public audience.</x:v>
       </x:c>
@@ -3846,7 +3867,7 @@
       <x:c r="D26" s="8" t="str">
         <x:v>U5 H6; U5 App H; U5 App I</x:v>
       </x:c>
-      <x:c r="E26" s="8" t="str"/>
+      <x:c r="E26" s="8"/>
       <x:c r="F26" s="7" t="str">
         <x:v>Discussion and CER.</x:v>
       </x:c>
@@ -3864,7 +3885,7 @@
       <x:c r="D27" s="8" t="str">
         <x:v>U5 H7; U5 App J; U5 App K; U5 App L</x:v>
       </x:c>
-      <x:c r="E27" s="8" t="str"/>
+      <x:c r="E27" s="8"/>
       <x:c r="F27" s="7" t="str">
         <x:v>Conclusion and full draft assembly.</x:v>
       </x:c>
@@ -3882,7 +3903,7 @@
       <x:c r="D28" s="8" t="str">
         <x:v>U5 H8; U5 H9; U5 App M; U5 App N</x:v>
       </x:c>
-      <x:c r="E28" s="8" t="str"/>
+      <x:c r="E28" s="8"/>
       <x:c r="F28" s="7" t="str">
         <x:v>Peer review; finalize event logistics, technology, accessibility, and assessment workflow.</x:v>
       </x:c>
@@ -3901,7 +3922,7 @@
         <x:v>U5 H10; U5 H11; U5 App O</x:v>
       </x:c>
       <x:c r="E29" s="8" t="str">
-        <x:v>U5 App Q</x:v>
+        <x:v>U5 App Q; U6 App L</x:v>
       </x:c>
       <x:c r="F29" s="7" t="str">
         <x:v>Presentation design and practice.</x:v>
@@ -3920,7 +3941,9 @@
       <x:c r="D30" s="8" t="str">
         <x:v>U6 H1; U6 H2; U6 H3; U6 App A; U6 App B; U6 App C</x:v>
       </x:c>
-      <x:c r="E30" s="8" t="str"/>
+      <x:c r="E30" s="8" t="str">
+        <x:v>U6 App L</x:v>
+      </x:c>
       <x:c r="F30" s="7" t="str">
         <x:v>Presentation readiness and message refinement.</x:v>
       </x:c>
@@ -3938,7 +3961,9 @@
       <x:c r="D31" s="8" t="str">
         <x:v>U6 H4; U6 H5; U6 H6; U6 App D; U6 App E</x:v>
       </x:c>
-      <x:c r="E31" s="8" t="str"/>
+      <x:c r="E31" s="8" t="str">
+        <x:v>U6 App L</x:v>
+      </x:c>
       <x:c r="F31" s="7" t="str">
         <x:v>Practice presentations and audience adaptation.</x:v>
       </x:c>
@@ -3956,7 +3981,9 @@
       <x:c r="D32" s="8" t="str">
         <x:v>U6 H7; U6 H8; U6 H9; U6 App F; U6 App G; U6 App H</x:v>
       </x:c>
-      <x:c r="E32" s="8" t="str"/>
+      <x:c r="E32" s="8" t="str">
+        <x:v>U6 App L</x:v>
+      </x:c>
       <x:c r="F32" s="7" t="str">
         <x:v>Q&amp;A preparation and evidence defense.</x:v>
       </x:c>
@@ -3975,7 +4002,7 @@
         <x:v>U6 H10; U6 H11; U6 H12</x:v>
       </x:c>
       <x:c r="E33" s="8" t="str">
-        <x:v>U6 App I; U6 App J; U6 App K</x:v>
+        <x:v>U6 App I; U6 App J; U6 App K; U6 App L</x:v>
       </x:c>
       <x:c r="F33" s="7" t="str">
         <x:v>Final showcase preparation.</x:v>
@@ -5005,19 +5032,19 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="4" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C1" s="4" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="s">
+      <x:c r="D1" s="4" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="s">
+      <x:c r="E1" s="4" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="D1" s="4" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E1" s="4" t="s">
-        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -5025,81 +5052,81 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C2" s="5" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D2" s="5" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C2" s="5" t="s">
+      <x:c r="E2" s="5" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="D2" s="5" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="E2" s="5" t="s">
-        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D3" s="5" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="C3" s="5" t="s">
+      <x:c r="E3" s="5" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="D3" s="5" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E3" s="5" t="s">
-        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="C4" s="5" t="s">
+      <x:c r="E4" s="5" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="s">
-        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="s">
+      <x:c r="E5" s="5" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="E5" s="5" t="s">
-        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="s">
-        <x:v>96</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
         <x:v>Student Handouts 1-11; Appendixes A-O and Q-S; Unit 6 Appendix L is the final oral rubric</x:v>
@@ -5107,19 +5134,19 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
         <x:v>Presentation, required public showcase, Q&amp;A, reflection, portfolio, and next steps</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1"/>
@@ -6118,10 +6145,10 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -6129,7 +6156,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6137,7 +6164,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -6145,7 +6172,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6153,7 +6180,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6161,7 +6188,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -6174,18 +6201,18 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="5" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="10">

--- a/Teacher Resources (Start Here)/06_STARLAB_Master_Print_Packet_Index.xlsx
+++ b/Teacher Resources (Start Here)/06_STARLAB_Master_Print_Packet_Index.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rc75939a0b50f4161"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print Packet Index" sheetId="2" r:id="Ra6aee84c7ee744ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Print Queue" sheetId="3" r:id="Rffd4691c09f041ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Unit" sheetId="4" r:id="R1bb651d7f797403d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Type Key" sheetId="5" r:id="R7efaf8d206594452"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R4546ef5cb1334b10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print Packet Index" sheetId="2" r:id="R7410611f7bc04cdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Print Queue" sheetId="3" r:id="R4b761042eeae4ab1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Unit" sheetId="4" r:id="R2db690687d6f42a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Type Key" sheetId="5" r:id="R50b6e8cc0b024e72"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -334,9 +334,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">The unit folder(s) where the required handouts/appendixes live.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Materials students should have for the lesson or lesson sequence.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">H</x:t>
@@ -658,7 +655,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="str">
-        <x:v>This spreadsheet separates required student copies from optional or teacher-reference materials and distinguishes primary teaching moments from later revisit use.</x:v>
+        <x:v>This spreadsheet separates required print materials from optional or teacher-reference materials and distinguishes primary teaching moments from later revisit use.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1769,12 +1766,9 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="G3" s="8" t="str">
-        <x:v>Unit 1 Student Handout 3: Research Interest Inventory
-Unit 1 Student Handout 6: From Topic to Research Question
-Unit 1 Student Handout 7: Question Quality Test
-Unit 1 Student Handout 8: Preliminary Project Pitch
-Unit 1 Appendix E: Strong vs. Weak Research Questions
-Unit 1 Appendix G: Engineering Design Problem Guide</x:v>
+        <x:v>Week 2 required packet (shared with Deck 4):
+Unit 1 Student Handouts 5-8
+Unit 1 Appendices D-H</x:v>
       </x:c>
       <x:c r="H3" s="8" t="str">
         <x:v>Unit 1 Appendix I: Optional Project Card Sorting Activity
@@ -1846,10 +1840,9 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="G5" s="8" t="str">
-        <x:v>Week 2 required:
-Unit 1 Student Handout 5: Experimental Design Practice
-Unit 1 Appendix D: Experimental Design Vocabulary
-Unit 1 Appendix G: Engineering Design Problem Guide
+        <x:v>Week 2 required packet (shared with Deck 2):
+Unit 1 Student Handouts 5-8
+Unit 1 Appendices D-H
 Week 3 revisit required:
 Unit 2 Student Handout 3: Hypothesis and Design Criteria Builder
 Unit 2 Student Handout 4: Variables, Controls, Criteria, and Constraints Organizer
@@ -3387,7 +3380,7 @@
         <x:v>Deck Use</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>Required Student Copies</x:v>
+        <x:v>Required Print Materials</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
         <x:v>Optional / Teacher Reference</x:v>
@@ -6187,8 +6180,8 @@
       <x:c r="A6" s="5" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>104</x:v>
+      <x:c r="B6" s="5" t="str">
+        <x:v>Materials that must be available for the lesson or lesson sequence. This may include student copies and required teacher references.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -6201,18 +6194,18 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="s">
-        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="5" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="10">

--- a/Teacher Resources (Start Here)/06_STARLAB_Master_Print_Packet_Index.xlsx
+++ b/Teacher Resources (Start Here)/06_STARLAB_Master_Print_Packet_Index.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R4546ef5cb1334b10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print Packet Index" sheetId="2" r:id="R7410611f7bc04cdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Print Queue" sheetId="3" r:id="R4b761042eeae4ab1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Unit" sheetId="4" r:id="R2db690687d6f42a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Type Key" sheetId="5" r:id="R50b6e8cc0b024e72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R845a2177e3104e10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print Packet Index" sheetId="2" r:id="Rdb266d3317d949fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Print Queue" sheetId="3" r:id="R987c325b9d1a4acc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Unit" sheetId="4" r:id="Rd23e5dee6f9e469a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Type Key" sheetId="5" r:id="R60bb5e3184c54535"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -198,9 +198,6 @@
 Unit 5 Appendix N: Scientific Report Rubric</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Draft 1 of student scientific reports</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Use once students have complete drafts.</x:t>
   </x:si>
   <x:si>
@@ -283,9 +280,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Decks 6–9</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Student Handouts 1–19; Appendixes A–U</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Weeks 17–20</x:t>
@@ -1953,7 +1947,8 @@
         <x:v>Later optional / teacher reference:
 Unit 3 Student Handout 9: Weekly Progress Check-In
 Unit 3 Student Handout 19: Research Journal Self-Assessment
-Unit 3 Appendix Q: File and Data Organization Standards</x:v>
+Unit 3 Appendix Q: File and Data Organization Standards
+Unit 3 Appendix V: Research Journal Rubric (teacher scoring reference)</x:v>
       </x:c>
       <x:c r="I8" s="8" t="str">
         <x:v>Introduce journal setup in Week 5; revisit documentation routines throughout Unit 3.</x:v>
@@ -2231,11 +2226,12 @@
       <x:c r="G16" s="8" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H16" s="8" t="s">
+      <x:c r="H16" s="8" t="str">
+        <x:v>Draft 1 of student scientific reports
+Unit 5 Appendix T: Peer Review Quality Rubric (use when locally scored)</x:v>
+      </x:c>
+      <x:c r="I16" s="8" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="I16" s="8" t="s">
-        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="66" hidden="0" customHeight="1">
@@ -2243,10 +2239,10 @@
         <x:v>16.0</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C17" s="5" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="C17" s="5" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
         <x:v>Unit 5 / Week 28</x:v>
@@ -2255,7 +2251,7 @@
         <x:v>Unit 6 / Week 32</x:v>
       </x:c>
       <x:c r="F17" s="8" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G17" s="8" t="str">
         <x:v>Unit 5 Student Handout 10: Presentation Planning Guide
@@ -2268,7 +2264,7 @@
 Unit 6 Appendices I-K (teacher event references)</x:v>
       </x:c>
       <x:c r="I17" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -2276,10 +2272,10 @@
         <x:v>17.0</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C18" s="5" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="C18" s="5" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="D18" s="8" t="str">
         <x:v>Unit 6 / Week 29</x:v>
@@ -2288,7 +2284,7 @@
         <x:v>Unit 5 / Week 28 preview; Unit 6 / Week 30 revisit</x:v>
       </x:c>
       <x:c r="F18" s="8" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G18" s="8" t="str">
         <x:v>Unit 5 Student Handouts 10-11
@@ -2307,10 +2303,10 @@
         <x:v>18.0</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C19" s="5" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="C19" s="5" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="D19" s="8" t="str">
         <x:v>Unit 6 / Week 31</x:v>
@@ -2319,7 +2315,7 @@
         <x:v>Unit 6 / Week 32</x:v>
       </x:c>
       <x:c r="F19" s="8" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G19" s="8" t="str">
         <x:v>Week 31 required:
@@ -2346,17 +2342,17 @@
         <x:v>19.0</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C20" s="5" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="C20" s="5" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="D20" s="8" t="str">
         <x:v>Unit 6 / Week 34</x:v>
       </x:c>
       <x:c r="E20" s="8" t="str"/>
       <x:c r="F20" s="8" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G20" s="8" t="str">
         <x:v>Unit 6 Student Handout 15: Final Research Process Reflection
@@ -3482,7 +3478,9 @@
       <x:c r="D6" s="8" t="str">
         <x:v>U3 H1; U3 H2; U3 H3; U3 App A; U3 App B; U3 App C</x:v>
       </x:c>
-      <x:c r="E6" s="8"/>
+      <x:c r="E6" s="8" t="str">
+        <x:v>U3 App V</x:v>
+      </x:c>
       <x:c r="F6" s="7" t="str">
         <x:v>Pilot test plan, journal setup, first entries.</x:v>
       </x:c>
@@ -3617,7 +3615,7 @@
         <x:v>U3 H14; U3 App N</x:v>
       </x:c>
       <x:c r="E13" s="8" t="str">
-        <x:v>U3 App O</x:v>
+        <x:v>U3 App O; U3 App V</x:v>
       </x:c>
       <x:c r="F13" s="7" t="str">
         <x:v>Mid-project progress report.</x:v>
@@ -3693,7 +3691,7 @@
         <x:v>U3 H18; U3 H19</x:v>
       </x:c>
       <x:c r="E17" s="8" t="str">
-        <x:v>U3 App S; U3 App T; U3 App U</x:v>
+        <x:v>U3 App S; U3 App T; U3 App U; U3 App V</x:v>
       </x:c>
       <x:c r="F17" s="7" t="str">
         <x:v>Readiness for Unit 4 analysis.</x:v>
@@ -3896,7 +3894,9 @@
       <x:c r="D28" s="8" t="str">
         <x:v>U5 H8; U5 H9; U5 App M; U5 App N</x:v>
       </x:c>
-      <x:c r="E28" s="8"/>
+      <x:c r="E28" s="8" t="str">
+        <x:v>U5 App T</x:v>
+      </x:c>
       <x:c r="F28" s="7" t="str">
         <x:v>Peer review; finalize event logistics, technology, accessibility, and assessment workflow.</x:v>
       </x:c>
@@ -5025,19 +5025,19 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="4" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="s">
+      <x:c r="C1" s="4" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="s">
+      <x:c r="D1" s="4" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="D1" s="4" t="s">
+      <x:c r="E1" s="4" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="E1" s="4" t="s">
-        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -5045,16 +5045,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C2" s="5" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="C2" s="5" t="s">
+      <x:c r="D2" s="5" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D2" s="5" t="s">
+      <x:c r="E2" s="5" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="E2" s="5" t="s">
-        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -5062,16 +5062,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C3" s="5" t="s">
+      <x:c r="D3" s="5" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D3" s="5" t="s">
+      <x:c r="E3" s="5" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="E3" s="5" t="s">
-        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -5079,16 +5079,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="C4" s="5" t="s">
+      <x:c r="D4" s="5" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="s">
-        <x:v>87</x:v>
+      <x:c r="E4" s="5" t="str">
+        <x:v>Student Handouts 1-19; Appendixes A-V</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -5096,16 +5096,16 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="s">
+      <x:c r="E5" s="5" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E5" s="5" t="s">
-        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -5113,33 +5113,33 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="E6" s="5" t="str">
-        <x:v>Student Handouts 1-11; Appendixes A-O and Q-S; Unit 6 Appendix L is the final oral rubric</x:v>
+        <x:v>Student Handouts 1-11; Appendixes A-O and Q-T; Unit 6 Appendix L is the final oral rubric</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="5" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
         <x:v>Presentation, required public showcase, Q&amp;A, reflection, portfolio, and next steps</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1"/>
@@ -6138,10 +6138,10 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -6149,7 +6149,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6157,7 +6157,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -6165,7 +6165,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6173,7 +6173,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6194,18 +6194,18 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="5" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
